--- a/result/xlsx/ecg_analysisresults1.xlsx
+++ b/result/xlsx/ecg_analysisresults1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>rat_number</t>
   </si>
@@ -35,6 +35,54 @@
   </si>
   <si>
     <t>pat_LAS_ms</t>
+  </si>
+  <si>
+    <t>norm_skewness</t>
+  </si>
+  <si>
+    <t>norm_kurtosis</t>
+  </si>
+  <si>
+    <t>norm_mean</t>
+  </si>
+  <si>
+    <t>norm_std</t>
+  </si>
+  <si>
+    <t>norm_QRSon</t>
+  </si>
+  <si>
+    <t>norm_QRSoff</t>
+  </si>
+  <si>
+    <t>norm_ratio_cwt_power</t>
+  </si>
+  <si>
+    <t>norm_ratio_psd_power</t>
+  </si>
+  <si>
+    <t>pat_skewness</t>
+  </si>
+  <si>
+    <t>pat_kurtosis</t>
+  </si>
+  <si>
+    <t>pat_mean</t>
+  </si>
+  <si>
+    <t>pat_std</t>
+  </si>
+  <si>
+    <t>pat_QRSon</t>
+  </si>
+  <si>
+    <t>pat_QRSoff</t>
+  </si>
+  <si>
+    <t>pat_ratio_cwt_power</t>
+  </si>
+  <si>
+    <t>pat_ratio_psd_power</t>
   </si>
 </sst>
 </file>
@@ -366,10 +414,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:W10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:23">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -391,96 +439,528 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:23">
       <c r="A2">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B2">
-        <v>23.84</v>
+        <v>33.92</v>
       </c>
       <c r="E2">
-        <v>26.08</v>
+        <v>26.88</v>
+      </c>
+      <c r="H2">
+        <v>-2.899867333218813</v>
+      </c>
+      <c r="I2">
+        <v>9.721385055590241</v>
+      </c>
+      <c r="J2">
+        <v>-0.0005057746726680605</v>
+      </c>
+      <c r="K2">
+        <v>0.04542367099613078</v>
+      </c>
+      <c r="L2">
+        <v>283</v>
+      </c>
+      <c r="M2">
+        <v>495</v>
+      </c>
+      <c r="N2">
+        <v>0.001076421813969865</v>
+      </c>
+      <c r="O2">
+        <v>8.069272802326366E-05</v>
+      </c>
+      <c r="P2">
+        <v>-0.9779293282613776</v>
+      </c>
+      <c r="Q2">
+        <v>2.182486788253798</v>
+      </c>
+      <c r="R2">
+        <v>-0.004363911302907359</v>
+      </c>
+      <c r="S2">
+        <v>0.0263994478463294</v>
+      </c>
+      <c r="T2">
+        <v>280</v>
+      </c>
+      <c r="U2">
+        <v>448</v>
+      </c>
+      <c r="V2">
+        <v>0.00167015716083882</v>
+      </c>
+      <c r="W2">
+        <v>9.975010102588446E-07</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:23">
       <c r="A3">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B3">
-        <v>23.84</v>
+        <v>0.64</v>
       </c>
       <c r="E3">
-        <v>26.08</v>
+        <v>31.68</v>
+      </c>
+      <c r="H3">
+        <v>3.54143453200964</v>
+      </c>
+      <c r="I3">
+        <v>10.93671012224731</v>
+      </c>
+      <c r="J3">
+        <v>0.006152862934176771</v>
+      </c>
+      <c r="K3">
+        <v>0.02001143110482368</v>
+      </c>
+      <c r="L3">
+        <v>9</v>
+      </c>
+      <c r="M3">
+        <v>13</v>
+      </c>
+      <c r="N3">
+        <v>0.4182716515677896</v>
+      </c>
+      <c r="O3">
+        <v>0.6085663232933495</v>
+      </c>
+      <c r="P3">
+        <v>-0.4701879465824741</v>
+      </c>
+      <c r="Q3">
+        <v>-0.128777879607834</v>
+      </c>
+      <c r="R3">
+        <v>0.0043624705884483</v>
+      </c>
+      <c r="S3">
+        <v>0.02615676910441542</v>
+      </c>
+      <c r="T3">
+        <v>194</v>
+      </c>
+      <c r="U3">
+        <v>392</v>
+      </c>
+      <c r="V3">
+        <v>0.00157776351389033</v>
+      </c>
+      <c r="W3">
+        <v>0.0002506909617677897</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:23">
       <c r="A4">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B4">
-        <v>23.84</v>
+        <v>28.96</v>
       </c>
       <c r="E4">
-        <v>26.08</v>
+        <v>41.92</v>
+      </c>
+      <c r="H4">
+        <v>-2.77723222644816</v>
+      </c>
+      <c r="I4">
+        <v>8.271323782126242</v>
+      </c>
+      <c r="J4">
+        <v>-0.001125237710761263</v>
+      </c>
+      <c r="K4">
+        <v>0.04011653483665924</v>
+      </c>
+      <c r="L4">
+        <v>263</v>
+      </c>
+      <c r="M4">
+        <v>444</v>
+      </c>
+      <c r="N4">
+        <v>0.0009559946905686583</v>
+      </c>
+      <c r="O4">
+        <v>5.098484324585793E-05</v>
+      </c>
+      <c r="P4">
+        <v>-0.4558619838913777</v>
+      </c>
+      <c r="Q4">
+        <v>3.497885149873459</v>
+      </c>
+      <c r="R4">
+        <v>-0.0009722611824588622</v>
+      </c>
+      <c r="S4">
+        <v>0.045073402099077</v>
+      </c>
+      <c r="T4">
+        <v>250</v>
+      </c>
+      <c r="U4">
+        <v>512</v>
+      </c>
+      <c r="V4">
+        <v>0.0001182461047910147</v>
+      </c>
+      <c r="W4">
+        <v>6.507643445565623E-06</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:23">
       <c r="A5">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B5">
-        <v>23.84</v>
+        <v>22.24</v>
       </c>
       <c r="E5">
-        <v>26.08</v>
+        <v>41.92</v>
+      </c>
+      <c r="H5">
+        <v>-2.69461976916788</v>
+      </c>
+      <c r="I5">
+        <v>9.676995761093707</v>
+      </c>
+      <c r="J5">
+        <v>-0.0263797623521039</v>
+      </c>
+      <c r="K5">
+        <v>0.01717142700674925</v>
+      </c>
+      <c r="L5">
+        <v>310</v>
+      </c>
+      <c r="M5">
+        <v>449</v>
+      </c>
+      <c r="N5">
+        <v>0.001085385171696151</v>
+      </c>
+      <c r="O5">
+        <v>1.888844924353825E-05</v>
+      </c>
+      <c r="P5">
+        <v>-0.2039312829489724</v>
+      </c>
+      <c r="Q5">
+        <v>-0.5268639423736152</v>
+      </c>
+      <c r="R5">
+        <v>0.01164261831066356</v>
+      </c>
+      <c r="S5">
+        <v>0.0133176097571202</v>
+      </c>
+      <c r="T5">
+        <v>250</v>
+      </c>
+      <c r="U5">
+        <v>512</v>
+      </c>
+      <c r="V5">
+        <v>0.01032336240355951</v>
+      </c>
+      <c r="W5">
+        <v>0.003036598891285055</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:23">
       <c r="A6">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B6">
-        <v>23.84</v>
+        <v>69.28</v>
       </c>
       <c r="E6">
-        <v>26.08</v>
+        <v>38.72</v>
+      </c>
+      <c r="H6">
+        <v>0.215865851334249</v>
+      </c>
+      <c r="I6">
+        <v>5.903662089284619</v>
+      </c>
+      <c r="J6">
+        <v>-0.00405373395980647</v>
+      </c>
+      <c r="K6">
+        <v>0.01832153532930451</v>
+      </c>
+      <c r="L6">
+        <v>281</v>
+      </c>
+      <c r="M6">
+        <v>714</v>
+      </c>
+      <c r="N6">
+        <v>0.000174026805833017</v>
+      </c>
+      <c r="O6">
+        <v>1.430257899224928E-06</v>
+      </c>
+      <c r="P6">
+        <v>0.070551576387749</v>
+      </c>
+      <c r="Q6">
+        <v>1.595467083869298</v>
+      </c>
+      <c r="R6">
+        <v>-0.00283471853904798</v>
+      </c>
+      <c r="S6">
+        <v>0.01670803947770898</v>
+      </c>
+      <c r="T6">
+        <v>230</v>
+      </c>
+      <c r="U6">
+        <v>472</v>
+      </c>
+      <c r="V6">
+        <v>0.0008170842545593581</v>
+      </c>
+      <c r="W6">
+        <v>9.071069645761259E-05</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:23">
       <c r="A7">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B7">
-        <v>23.84</v>
+        <v>66.72</v>
       </c>
       <c r="E7">
-        <v>26.08</v>
+        <v>21.92</v>
+      </c>
+      <c r="H7">
+        <v>1.47532022712523</v>
+      </c>
+      <c r="I7">
+        <v>5.603036648086595</v>
+      </c>
+      <c r="J7">
+        <v>0.01104627426151033</v>
+      </c>
+      <c r="K7">
+        <v>0.02588833768292081</v>
+      </c>
+      <c r="L7">
+        <v>298</v>
+      </c>
+      <c r="M7">
+        <v>715</v>
+      </c>
+      <c r="N7">
+        <v>0.0005985008963011998</v>
+      </c>
+      <c r="O7">
+        <v>7.346784057291776E-05</v>
+      </c>
+      <c r="P7">
+        <v>1.63879794432896</v>
+      </c>
+      <c r="Q7">
+        <v>3.680408734906032</v>
+      </c>
+      <c r="R7">
+        <v>-0.0007390241947077314</v>
+      </c>
+      <c r="S7">
+        <v>0.02622957800575567</v>
+      </c>
+      <c r="T7">
+        <v>306</v>
+      </c>
+      <c r="U7">
+        <v>443</v>
+      </c>
+      <c r="V7">
+        <v>0.000783745494855988</v>
+      </c>
+      <c r="W7">
+        <v>3.598938910618145E-06</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:23">
       <c r="A8">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B8">
-        <v>23.84</v>
+        <v>31.84</v>
       </c>
       <c r="E8">
-        <v>26.08</v>
+        <v>37.6</v>
+      </c>
+      <c r="H8">
+        <v>-0.9987980320040449</v>
+      </c>
+      <c r="I8">
+        <v>4.55020245618759</v>
+      </c>
+      <c r="J8">
+        <v>0.008097999209896307</v>
+      </c>
+      <c r="K8">
+        <v>0.02780383690816041</v>
+      </c>
+      <c r="L8">
+        <v>284</v>
+      </c>
+      <c r="M8">
+        <v>483</v>
+      </c>
+      <c r="N8">
+        <v>0.001105391340859731</v>
+      </c>
+      <c r="O8">
+        <v>6.462046082414456E-05</v>
+      </c>
+      <c r="P8">
+        <v>-1.018823057125054</v>
+      </c>
+      <c r="Q8">
+        <v>2.53386126706738</v>
+      </c>
+      <c r="R8">
+        <v>-0.001378601536630058</v>
+      </c>
+      <c r="S8">
+        <v>0.02624964957769141</v>
+      </c>
+      <c r="T8">
+        <v>250</v>
+      </c>
+      <c r="U8">
+        <v>485</v>
+      </c>
+      <c r="V8">
+        <v>0.001771337693171329</v>
+      </c>
+      <c r="W8">
+        <v>7.016009163626126E-06</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:23">
       <c r="A9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9">
-        <v>23.84</v>
+        <v>20.96</v>
       </c>
       <c r="E9">
-        <v>26.08</v>
+        <v>24.32</v>
+      </c>
+      <c r="H9">
+        <v>-0.5127518845208312</v>
+      </c>
+      <c r="I9">
+        <v>3.92942857786977</v>
+      </c>
+      <c r="J9">
+        <v>-0.001655689757182227</v>
+      </c>
+      <c r="K9">
+        <v>0.01653547676976924</v>
+      </c>
+      <c r="L9">
+        <v>275</v>
+      </c>
+      <c r="M9">
+        <v>406</v>
+      </c>
+      <c r="N9">
+        <v>1.998416085115057E-05</v>
+      </c>
+      <c r="O9">
+        <v>1.26804805420207E-06</v>
+      </c>
+      <c r="P9">
+        <v>-0.5051474735511229</v>
+      </c>
+      <c r="Q9">
+        <v>1.241155044600236</v>
+      </c>
+      <c r="R9">
+        <v>-0.002242444832444879</v>
+      </c>
+      <c r="S9">
+        <v>0.0296856848273458</v>
+      </c>
+      <c r="T9">
+        <v>257</v>
+      </c>
+      <c r="U9">
+        <v>409</v>
+      </c>
+      <c r="V9">
+        <v>0.0002904266264390794</v>
+      </c>
+      <c r="W9">
+        <v>2.081990741482817E-05</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:23">
       <c r="A10">
         <v>18</v>
       </c>
@@ -489,6 +969,54 @@
       </c>
       <c r="E10">
         <v>26.08</v>
+      </c>
+      <c r="H10">
+        <v>0.0465395148424246</v>
+      </c>
+      <c r="I10">
+        <v>3.014935901185414</v>
+      </c>
+      <c r="J10">
+        <v>-0.02345711087338977</v>
+      </c>
+      <c r="K10">
+        <v>0.05128646321283863</v>
+      </c>
+      <c r="L10">
+        <v>257</v>
+      </c>
+      <c r="M10">
+        <v>406</v>
+      </c>
+      <c r="N10">
+        <v>0.0002525429438186194</v>
+      </c>
+      <c r="O10">
+        <v>2.47199726589059E-05</v>
+      </c>
+      <c r="P10">
+        <v>0.5559587376960631</v>
+      </c>
+      <c r="Q10">
+        <v>3.591900105662238</v>
+      </c>
+      <c r="R10">
+        <v>-0.001428498674354127</v>
+      </c>
+      <c r="S10">
+        <v>0.03236886816824928</v>
+      </c>
+      <c r="T10">
+        <v>272</v>
+      </c>
+      <c r="U10">
+        <v>435</v>
+      </c>
+      <c r="V10">
+        <v>0.001505463485696217</v>
+      </c>
+      <c r="W10">
+        <v>6.529529794116115E-06</v>
       </c>
     </row>
   </sheetData>

--- a/result/xlsx/ecg_analysisresults1.xlsx
+++ b/result/xlsx/ecg_analysisresults1.xlsx
@@ -498,6 +498,12 @@
       <c r="E2">
         <v>26.88</v>
       </c>
+      <c r="F2">
+        <v>0.01196029053129781</v>
+      </c>
+      <c r="G2">
+        <v>71.84</v>
+      </c>
       <c r="H2">
         <v>-2.899867333218813</v>
       </c>
@@ -557,6 +563,12 @@
       <c r="E3">
         <v>31.68</v>
       </c>
+      <c r="F3">
+        <v>0.01495905008353151</v>
+      </c>
+      <c r="G3">
+        <v>62.88</v>
+      </c>
       <c r="H3">
         <v>3.54143453200964</v>
       </c>
@@ -616,6 +628,12 @@
       <c r="E4">
         <v>41.92</v>
       </c>
+      <c r="F4">
+        <v>0.02847806372329953</v>
+      </c>
+      <c r="G4">
+        <v>82.08</v>
+      </c>
       <c r="H4">
         <v>-2.77723222644816</v>
       </c>
@@ -675,6 +693,12 @@
       <c r="E5">
         <v>41.92</v>
       </c>
+      <c r="F5">
+        <v>0.02847806372329953</v>
+      </c>
+      <c r="G5">
+        <v>82.08</v>
+      </c>
       <c r="H5">
         <v>-2.69461976916788</v>
       </c>
@@ -734,6 +758,12 @@
       <c r="E6">
         <v>38.72</v>
       </c>
+      <c r="F6">
+        <v>0.01993907157170043</v>
+      </c>
+      <c r="G6">
+        <v>75.67999999999999</v>
+      </c>
       <c r="H6">
         <v>0.215865851334249</v>
       </c>
@@ -793,6 +823,12 @@
       <c r="E7">
         <v>21.92</v>
       </c>
+      <c r="F7">
+        <v>0.01404484875193865</v>
+      </c>
+      <c r="G7">
+        <v>71.04000000000001</v>
+      </c>
       <c r="H7">
         <v>1.47532022712523</v>
       </c>
@@ -852,6 +888,12 @@
       <c r="E8">
         <v>37.6</v>
       </c>
+      <c r="F8">
+        <v>0.01587000039557492</v>
+      </c>
+      <c r="G8">
+        <v>77.75999999999999</v>
+      </c>
       <c r="H8">
         <v>-0.9987980320040449</v>
       </c>
@@ -911,6 +953,12 @@
       <c r="E9">
         <v>24.32</v>
       </c>
+      <c r="F9">
+        <v>0.01553641479704467</v>
+      </c>
+      <c r="G9">
+        <v>65.60000000000001</v>
+      </c>
       <c r="H9">
         <v>-0.5127518845208312</v>
       </c>
@@ -969,6 +1017,12 @@
       </c>
       <c r="E10">
         <v>26.08</v>
+      </c>
+      <c r="F10">
+        <v>0.02175061395073356</v>
+      </c>
+      <c r="G10">
+        <v>69.76000000000001</v>
       </c>
       <c r="H10">
         <v>0.0465395148424246</v>

--- a/result/xlsx/ecg_analysisresults1.xlsx
+++ b/result/xlsx/ecg_analysisresults1.xlsx
@@ -496,25 +496,25 @@
         <v>33.92</v>
       </c>
       <c r="E2">
-        <v>26.88</v>
+        <v>26.08</v>
       </c>
       <c r="F2">
-        <v>0.01196029053129781</v>
+        <v>0.01289097725725355</v>
       </c>
       <c r="G2">
-        <v>71.84</v>
+        <v>70.88</v>
       </c>
       <c r="H2">
-        <v>-2.899867333218813</v>
+        <v>-2.896416525808391</v>
       </c>
       <c r="I2">
-        <v>9.721385055590241</v>
+        <v>9.680644607493234</v>
       </c>
       <c r="J2">
-        <v>-0.0005057746726680605</v>
+        <v>-0.0004792050467676656</v>
       </c>
       <c r="K2">
-        <v>0.04542367099613078</v>
+        <v>0.0451034416093991</v>
       </c>
       <c r="L2">
         <v>283</v>
@@ -523,34 +523,34 @@
         <v>495</v>
       </c>
       <c r="N2">
-        <v>0.001076421813969865</v>
+        <v>0.00106316628233838</v>
       </c>
       <c r="O2">
-        <v>8.069272802326366E-05</v>
+        <v>7.401774184589742E-05</v>
       </c>
       <c r="P2">
-        <v>-0.9779293282613776</v>
+        <v>-0.9938436486225042</v>
       </c>
       <c r="Q2">
-        <v>2.182486788253798</v>
+        <v>2.252580888018167</v>
       </c>
       <c r="R2">
-        <v>-0.004363911302907359</v>
+        <v>-0.001712533510177653</v>
       </c>
       <c r="S2">
-        <v>0.0263994478463294</v>
+        <v>0.02942047582720344</v>
       </c>
       <c r="T2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="U2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="V2">
-        <v>0.00167015716083882</v>
+        <v>0.002233622324148771</v>
       </c>
       <c r="W2">
-        <v>9.975010102588446E-07</v>
+        <v>7.949197975276071E-07</v>
       </c>
     </row>
     <row r="3" spans="1:23">
@@ -558,64 +558,64 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>0.64</v>
+        <v>33.92</v>
       </c>
       <c r="E3">
-        <v>31.68</v>
+        <v>31.84</v>
       </c>
       <c r="F3">
-        <v>0.01495905008353151</v>
+        <v>0.01545207381696054</v>
       </c>
       <c r="G3">
-        <v>62.88</v>
+        <v>63.04</v>
       </c>
       <c r="H3">
-        <v>3.54143453200964</v>
+        <v>0.1709219072410759</v>
       </c>
       <c r="I3">
-        <v>10.93671012224731</v>
+        <v>8.435502017955752</v>
       </c>
       <c r="J3">
-        <v>0.006152862934176771</v>
+        <v>6.012526834551568E-06</v>
       </c>
       <c r="K3">
-        <v>0.02001143110482368</v>
+        <v>0.00306136076858581</v>
       </c>
       <c r="L3">
-        <v>9</v>
+        <v>283</v>
       </c>
       <c r="M3">
-        <v>13</v>
+        <v>495</v>
       </c>
       <c r="N3">
-        <v>0.4182716515677896</v>
+        <v>0.7707489539242163</v>
       </c>
       <c r="O3">
-        <v>0.6085663232933495</v>
+        <v>0.8469582015082</v>
       </c>
       <c r="P3">
-        <v>-0.4701879465824741</v>
+        <v>-0.6531175255708912</v>
       </c>
       <c r="Q3">
-        <v>-0.128777879607834</v>
+        <v>0.04973324219273456</v>
       </c>
       <c r="R3">
-        <v>0.0043624705884483</v>
+        <v>0.0007842691076640307</v>
       </c>
       <c r="S3">
-        <v>0.02615676910441542</v>
+        <v>0.02621870586511935</v>
       </c>
       <c r="T3">
         <v>194</v>
       </c>
       <c r="U3">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="V3">
-        <v>0.00157776351389033</v>
+        <v>0.002095761696200646</v>
       </c>
       <c r="W3">
-        <v>0.0002506909617677897</v>
+        <v>0.0002134785454252723</v>
       </c>
     </row>
     <row r="4" spans="1:23">
@@ -623,64 +623,64 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>28.96</v>
+        <v>29.44</v>
       </c>
       <c r="E4">
-        <v>41.92</v>
+        <v>42.72</v>
       </c>
       <c r="F4">
-        <v>0.02847806372329953</v>
+        <v>0.02632605363682696</v>
       </c>
       <c r="G4">
-        <v>82.08</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="H4">
-        <v>-2.77723222644816</v>
+        <v>-2.763760255502575</v>
       </c>
       <c r="I4">
-        <v>8.271323782126242</v>
+        <v>8.150483771559607</v>
       </c>
       <c r="J4">
-        <v>-0.001125237710761263</v>
+        <v>0.0009054076366170438</v>
       </c>
       <c r="K4">
-        <v>0.04011653483665924</v>
+        <v>0.04006048965267817</v>
       </c>
       <c r="L4">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="M4">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N4">
-        <v>0.0009559946905686583</v>
+        <v>0.0010938798109798</v>
       </c>
       <c r="O4">
-        <v>5.098484324585793E-05</v>
+        <v>4.658662661372531E-05</v>
       </c>
       <c r="P4">
-        <v>-0.4558619838913777</v>
+        <v>-0.573295102863713</v>
       </c>
       <c r="Q4">
-        <v>3.497885149873459</v>
+        <v>3.299146976909885</v>
       </c>
       <c r="R4">
-        <v>-0.0009722611824588622</v>
+        <v>-0.0005611501996359798</v>
       </c>
       <c r="S4">
-        <v>0.045073402099077</v>
+        <v>0.04546604662594152</v>
       </c>
       <c r="T4">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="U4">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="V4">
-        <v>0.0001182461047910147</v>
+        <v>0.000130485229243267</v>
       </c>
       <c r="W4">
-        <v>6.507643445565623E-06</v>
+        <v>5.18946581741653E-06</v>
       </c>
     </row>
     <row r="5" spans="1:23">
@@ -688,64 +688,64 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>22.24</v>
+        <v>130.08</v>
       </c>
       <c r="E5">
-        <v>41.92</v>
+        <v>0.64</v>
       </c>
       <c r="F5">
-        <v>0.02847806372329953</v>
+        <v>0.007744044185880387</v>
       </c>
       <c r="G5">
-        <v>82.08</v>
+        <v>2.24</v>
       </c>
       <c r="H5">
-        <v>-2.69461976916788</v>
+        <v>-2.676233833460888</v>
       </c>
       <c r="I5">
-        <v>9.676995761093707</v>
+        <v>9.324828360135674</v>
       </c>
       <c r="J5">
-        <v>-0.0263797623521039</v>
+        <v>-0.001336210726327087</v>
       </c>
       <c r="K5">
-        <v>0.01717142700674925</v>
+        <v>0.01199225032923227</v>
       </c>
       <c r="L5">
-        <v>310</v>
+        <v>75</v>
       </c>
       <c r="M5">
-        <v>449</v>
+        <v>888</v>
       </c>
       <c r="N5">
-        <v>0.001085385171696151</v>
+        <v>0.001860642979305037</v>
       </c>
       <c r="O5">
-        <v>1.888844924353825E-05</v>
+        <v>0.0001060854660824825</v>
       </c>
       <c r="P5">
-        <v>-0.2039312829489724</v>
+        <v>0.2833349811658236</v>
       </c>
       <c r="Q5">
-        <v>-0.5268639423736152</v>
+        <v>-0.651019863455593</v>
       </c>
       <c r="R5">
-        <v>0.01164261831066356</v>
+        <v>-0.00237870523854025</v>
       </c>
       <c r="S5">
-        <v>0.0133176097571202</v>
+        <v>0.01007664067017811</v>
       </c>
       <c r="T5">
-        <v>250</v>
+        <v>9</v>
       </c>
       <c r="U5">
-        <v>512</v>
+        <v>13</v>
       </c>
       <c r="V5">
-        <v>0.01032336240355951</v>
+        <v>0.0324972852338991</v>
       </c>
       <c r="W5">
-        <v>0.003036598891285055</v>
+        <v>0.008193209819591393</v>
       </c>
     </row>
     <row r="6" spans="1:23">
@@ -753,64 +753,64 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>69.28</v>
+        <v>71.36000000000001</v>
       </c>
       <c r="E6">
-        <v>38.72</v>
+        <v>43.84</v>
       </c>
       <c r="F6">
-        <v>0.01993907157170043</v>
+        <v>0.02114177073216123</v>
       </c>
       <c r="G6">
-        <v>75.67999999999999</v>
+        <v>74.72</v>
       </c>
       <c r="H6">
-        <v>0.215865851334249</v>
+        <v>0.3880093281308312</v>
       </c>
       <c r="I6">
-        <v>5.903662089284619</v>
+        <v>5.83878369435188</v>
       </c>
       <c r="J6">
-        <v>-0.00405373395980647</v>
+        <v>0.000123295968154055</v>
       </c>
       <c r="K6">
-        <v>0.01832153532930451</v>
+        <v>0.01854903067020648</v>
       </c>
       <c r="L6">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="M6">
-        <v>714</v>
+        <v>734</v>
       </c>
       <c r="N6">
-        <v>0.000174026805833017</v>
+        <v>0.0002536030870855325</v>
       </c>
       <c r="O6">
-        <v>1.430257899224928E-06</v>
+        <v>1.126256536824595E-06</v>
       </c>
       <c r="P6">
-        <v>0.070551576387749</v>
+        <v>0.2525813162014702</v>
       </c>
       <c r="Q6">
-        <v>1.595467083869298</v>
+        <v>1.68975823691552</v>
       </c>
       <c r="R6">
-        <v>-0.00283471853904798</v>
+        <v>-0.003164234607174515</v>
       </c>
       <c r="S6">
-        <v>0.01670803947770898</v>
+        <v>0.01721580724241833</v>
       </c>
       <c r="T6">
-        <v>230</v>
+        <v>192</v>
       </c>
       <c r="U6">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="V6">
-        <v>0.0008170842545593581</v>
+        <v>0.001009042593344173</v>
       </c>
       <c r="W6">
-        <v>9.071069645761259E-05</v>
+        <v>8.264577089035876E-05</v>
       </c>
     </row>
     <row r="7" spans="1:23">
@@ -818,64 +818,64 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>66.72</v>
+        <v>60.8</v>
       </c>
       <c r="E7">
-        <v>21.92</v>
+        <v>20.48</v>
       </c>
       <c r="F7">
-        <v>0.01404484875193865</v>
+        <v>0.01353403300712124</v>
       </c>
       <c r="G7">
-        <v>71.04000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="H7">
-        <v>1.47532022712523</v>
+        <v>1.411881921752367</v>
       </c>
       <c r="I7">
-        <v>5.603036648086595</v>
+        <v>5.345894788971245</v>
       </c>
       <c r="J7">
-        <v>0.01104627426151033</v>
+        <v>0.001338282323900944</v>
       </c>
       <c r="K7">
-        <v>0.02588833768292081</v>
+        <v>0.02677707265779925</v>
       </c>
       <c r="L7">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="M7">
-        <v>715</v>
+        <v>675</v>
       </c>
       <c r="N7">
-        <v>0.0005985008963011998</v>
+        <v>0.0004676391403885697</v>
       </c>
       <c r="O7">
-        <v>7.346784057291776E-05</v>
+        <v>8.755697705455358E-05</v>
       </c>
       <c r="P7">
-        <v>1.63879794432896</v>
+        <v>1.615654557059473</v>
       </c>
       <c r="Q7">
-        <v>3.680408734906032</v>
+        <v>3.510157423571511</v>
       </c>
       <c r="R7">
-        <v>-0.0007390241947077314</v>
+        <v>-3.765092836702344E-05</v>
       </c>
       <c r="S7">
-        <v>0.02622957800575567</v>
+        <v>0.02596240082470963</v>
       </c>
       <c r="T7">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="U7">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="V7">
-        <v>0.000783745494855988</v>
+        <v>0.0007689221297599104</v>
       </c>
       <c r="W7">
-        <v>3.598938910618145E-06</v>
+        <v>4.713266552054918E-06</v>
       </c>
     </row>
     <row r="8" spans="1:23">
@@ -883,64 +883,64 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>31.84</v>
+        <v>31.36</v>
       </c>
       <c r="E8">
-        <v>37.6</v>
+        <v>28.8</v>
       </c>
       <c r="F8">
-        <v>0.01587000039557492</v>
+        <v>0.01530785707419493</v>
       </c>
       <c r="G8">
-        <v>77.75999999999999</v>
+        <v>76.16000000000001</v>
       </c>
       <c r="H8">
-        <v>-0.9987980320040449</v>
+        <v>-0.8491643212964515</v>
       </c>
       <c r="I8">
-        <v>4.55020245618759</v>
+        <v>4.588932797821692</v>
       </c>
       <c r="J8">
-        <v>0.008097999209896307</v>
+        <v>-5.486300570091051E-05</v>
       </c>
       <c r="K8">
-        <v>0.02780383690816041</v>
+        <v>0.03051485408746376</v>
       </c>
       <c r="L8">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="M8">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="N8">
-        <v>0.001105391340859731</v>
+        <v>0.0008991856708976707</v>
       </c>
       <c r="O8">
-        <v>6.462046082414456E-05</v>
+        <v>9.798959221981582E-05</v>
       </c>
       <c r="P8">
-        <v>-1.018823057125054</v>
+        <v>-1.066599209025287</v>
       </c>
       <c r="Q8">
-        <v>2.53386126706738</v>
+        <v>2.526693676457811</v>
       </c>
       <c r="R8">
-        <v>-0.001378601536630058</v>
+        <v>-0.0003340442893269766</v>
       </c>
       <c r="S8">
-        <v>0.02624964957769141</v>
+        <v>0.02589477159034883</v>
       </c>
       <c r="T8">
-        <v>250</v>
+        <v>295</v>
       </c>
       <c r="U8">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="V8">
-        <v>0.001771337693171329</v>
+        <v>0.00218978612836585</v>
       </c>
       <c r="W8">
-        <v>7.016009163626126E-06</v>
+        <v>3.785571543126623E-06</v>
       </c>
     </row>
     <row r="9" spans="1:23">
@@ -948,64 +948,64 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>20.96</v>
+        <v>95.68000000000001</v>
       </c>
       <c r="E9">
-        <v>24.32</v>
+        <v>24.64</v>
       </c>
       <c r="F9">
-        <v>0.01553641479704467</v>
+        <v>0.0157436605672381</v>
       </c>
       <c r="G9">
-        <v>65.60000000000001</v>
+        <v>66.08</v>
       </c>
       <c r="H9">
-        <v>-0.5127518845208312</v>
+        <v>-0.8370450237240743</v>
       </c>
       <c r="I9">
-        <v>3.92942857786977</v>
+        <v>2.902781353520866</v>
       </c>
       <c r="J9">
-        <v>-0.001655689757182227</v>
+        <v>0.000113887776867466</v>
       </c>
       <c r="K9">
-        <v>0.01653547676976924</v>
+        <v>0.0150377916880895</v>
       </c>
       <c r="L9">
-        <v>275</v>
+        <v>248</v>
       </c>
       <c r="M9">
-        <v>406</v>
+        <v>846</v>
       </c>
       <c r="N9">
-        <v>1.998416085115057E-05</v>
+        <v>0.0004756831142825025</v>
       </c>
       <c r="O9">
-        <v>1.26804805420207E-06</v>
+        <v>1.660761501716177E-06</v>
       </c>
       <c r="P9">
-        <v>-0.5051474735511229</v>
+        <v>-0.4697787930459011</v>
       </c>
       <c r="Q9">
-        <v>1.241155044600236</v>
+        <v>1.386860669334919</v>
       </c>
       <c r="R9">
-        <v>-0.002242444832444879</v>
+        <v>0.0002831761142650475</v>
       </c>
       <c r="S9">
-        <v>0.0296856848273458</v>
+        <v>0.02996751436151743</v>
       </c>
       <c r="T9">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="U9">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="V9">
-        <v>0.0002904266264390794</v>
+        <v>0.0005012384472565072</v>
       </c>
       <c r="W9">
-        <v>2.081990741482817E-05</v>
+        <v>2.640774999893631E-05</v>
       </c>
     </row>
     <row r="10" spans="1:23">
@@ -1013,64 +1013,64 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>23.84</v>
+        <v>21.12</v>
       </c>
       <c r="E10">
-        <v>26.08</v>
+        <v>25.28</v>
       </c>
       <c r="F10">
-        <v>0.02175061395073356</v>
+        <v>0.02237448185504321</v>
       </c>
       <c r="G10">
-        <v>69.76000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H10">
-        <v>0.0465395148424246</v>
+        <v>0.2398255713248025</v>
       </c>
       <c r="I10">
-        <v>3.014935901185414</v>
+        <v>2.977885709940506</v>
       </c>
       <c r="J10">
-        <v>-0.02345711087338977</v>
+        <v>-0.0002912686382950547</v>
       </c>
       <c r="K10">
-        <v>0.05128646321283863</v>
+        <v>0.05153352390151887</v>
       </c>
       <c r="L10">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="M10">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="N10">
-        <v>0.0002525429438186194</v>
+        <v>0.001313834503265043</v>
       </c>
       <c r="O10">
-        <v>2.47199726589059E-05</v>
+        <v>4.909452615728609E-05</v>
       </c>
       <c r="P10">
-        <v>0.5559587376960631</v>
+        <v>0.587817596845857</v>
       </c>
       <c r="Q10">
-        <v>3.591900105662238</v>
+        <v>3.7259679338161</v>
       </c>
       <c r="R10">
-        <v>-0.001428498674354127</v>
+        <v>-0.0002239271328408037</v>
       </c>
       <c r="S10">
-        <v>0.03236886816824928</v>
+        <v>0.03210615986299115</v>
       </c>
       <c r="T10">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="U10">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="V10">
-        <v>0.001505463485696217</v>
+        <v>0.001024022373068393</v>
       </c>
       <c r="W10">
-        <v>6.529529794116115E-06</v>
+        <v>7.558357434712283E-06</v>
       </c>
     </row>
   </sheetData>

--- a/result/xlsx/ecg_analysisresults1.xlsx
+++ b/result/xlsx/ecg_analysisresults1.xlsx
@@ -495,6 +495,12 @@
       <c r="B2">
         <v>33.92</v>
       </c>
+      <c r="C2">
+        <v>0.03933095212484044</v>
+      </c>
+      <c r="D2">
+        <v>79.36</v>
+      </c>
       <c r="E2">
         <v>26.08</v>
       </c>
@@ -560,6 +566,12 @@
       <c r="B3">
         <v>33.92</v>
       </c>
+      <c r="C3">
+        <v>0.03933095212484044</v>
+      </c>
+      <c r="D3">
+        <v>79.36</v>
+      </c>
       <c r="E3">
         <v>31.84</v>
       </c>
@@ -625,6 +637,12 @@
       <c r="B4">
         <v>29.44</v>
       </c>
+      <c r="C4">
+        <v>0.03610792164320767</v>
+      </c>
+      <c r="D4">
+        <v>71.36000000000001</v>
+      </c>
       <c r="E4">
         <v>42.72</v>
       </c>
@@ -690,6 +708,12 @@
       <c r="B5">
         <v>130.08</v>
       </c>
+      <c r="C5">
+        <v>0.002469889499419557</v>
+      </c>
+      <c r="D5">
+        <v>142.24</v>
+      </c>
       <c r="E5">
         <v>0.64</v>
       </c>
@@ -755,6 +779,12 @@
       <c r="B6">
         <v>71.36000000000001</v>
       </c>
+      <c r="C6">
+        <v>0.007852700182600307</v>
+      </c>
+      <c r="D6">
+        <v>117.6</v>
+      </c>
       <c r="E6">
         <v>43.84</v>
       </c>
@@ -820,6 +850,12 @@
       <c r="B7">
         <v>60.8</v>
       </c>
+      <c r="C7">
+        <v>0.008212810720063609</v>
+      </c>
+      <c r="D7">
+        <v>108.16</v>
+      </c>
       <c r="E7">
         <v>20.48</v>
       </c>
@@ -885,6 +921,12 @@
       <c r="B8">
         <v>31.36</v>
       </c>
+      <c r="C8">
+        <v>0.03467166997865731</v>
+      </c>
+      <c r="D8">
+        <v>75.52000000000001</v>
+      </c>
       <c r="E8">
         <v>28.8</v>
       </c>
@@ -950,6 +992,12 @@
       <c r="B9">
         <v>95.68000000000001</v>
       </c>
+      <c r="C9">
+        <v>0.002617553316373425</v>
+      </c>
+      <c r="D9">
+        <v>135.52</v>
+      </c>
       <c r="E9">
         <v>24.64</v>
       </c>
@@ -1014,6 +1062,12 @@
       </c>
       <c r="B10">
         <v>21.12</v>
+      </c>
+      <c r="C10">
+        <v>0.04278861977265875</v>
+      </c>
+      <c r="D10">
+        <v>66.55999999999999</v>
       </c>
       <c r="E10">
         <v>25.28</v>

--- a/result/xlsx/ecg_analysisresults1.xlsx
+++ b/result/xlsx/ecg_analysisresults1.xlsx
@@ -414,7 +414,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W10"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:23">
@@ -490,640 +490,143 @@
     </row>
     <row r="2" spans="1:23">
       <c r="A2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B2">
-        <v>33.92</v>
+        <v>95.68000000000001</v>
       </c>
       <c r="C2">
-        <v>0.03933095212484044</v>
+        <v>0.002617553316373425</v>
       </c>
       <c r="D2">
-        <v>79.36</v>
+        <v>135.52</v>
       </c>
       <c r="E2">
-        <v>26.08</v>
+        <v>24.64</v>
       </c>
       <c r="F2">
-        <v>0.01289097725725355</v>
+        <v>0.0157436605672381</v>
       </c>
       <c r="G2">
-        <v>70.88</v>
+        <v>66.08</v>
       </c>
       <c r="H2">
-        <v>-2.896416525808391</v>
+        <v>-0.8370450237240743</v>
       </c>
       <c r="I2">
-        <v>9.680644607493234</v>
+        <v>2.902781353520866</v>
       </c>
       <c r="J2">
-        <v>-0.0004792050467676656</v>
+        <v>0.000113887776867466</v>
       </c>
       <c r="K2">
-        <v>0.0451034416093991</v>
+        <v>0.0150377916880895</v>
       </c>
       <c r="L2">
-        <v>283</v>
+        <v>248</v>
       </c>
       <c r="M2">
-        <v>495</v>
+        <v>846</v>
       </c>
       <c r="N2">
-        <v>0.00106316628233838</v>
+        <v>0.0004756831142825025</v>
       </c>
       <c r="O2">
-        <v>7.401774184589742E-05</v>
+        <v>1.660761501716177E-06</v>
       </c>
       <c r="P2">
-        <v>-0.9938436486225042</v>
+        <v>-0.4697787930459011</v>
       </c>
       <c r="Q2">
-        <v>2.252580888018167</v>
+        <v>1.386860669334919</v>
       </c>
       <c r="R2">
-        <v>-0.001712533510177653</v>
+        <v>0.0002831761142650475</v>
       </c>
       <c r="S2">
-        <v>0.02942047582720344</v>
+        <v>0.02996751436151743</v>
       </c>
       <c r="T2">
-        <v>279</v>
+        <v>258</v>
       </c>
       <c r="U2">
-        <v>442</v>
+        <v>412</v>
       </c>
       <c r="V2">
-        <v>0.002233622324148771</v>
+        <v>0.0005012384472565072</v>
       </c>
       <c r="W2">
-        <v>7.949197975276071E-07</v>
+        <v>2.640774999893631E-05</v>
       </c>
     </row>
     <row r="3" spans="1:23">
       <c r="A3">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B3">
-        <v>33.92</v>
+        <v>21.12</v>
       </c>
       <c r="C3">
-        <v>0.03933095212484044</v>
+        <v>0.04278861977265875</v>
       </c>
       <c r="D3">
-        <v>79.36</v>
+        <v>66.55999999999999</v>
       </c>
       <c r="E3">
-        <v>31.84</v>
+        <v>25.28</v>
       </c>
       <c r="F3">
-        <v>0.01545207381696054</v>
+        <v>0.02237448185504321</v>
       </c>
       <c r="G3">
-        <v>63.04</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H3">
-        <v>0.1709219072410759</v>
+        <v>0.2398255713248025</v>
       </c>
       <c r="I3">
-        <v>8.435502017955752</v>
+        <v>2.977885709940506</v>
       </c>
       <c r="J3">
-        <v>6.012526834551568E-06</v>
+        <v>-0.0002912686382950547</v>
       </c>
       <c r="K3">
-        <v>0.00306136076858581</v>
+        <v>0.05153352390151887</v>
       </c>
       <c r="L3">
         <v>283</v>
       </c>
       <c r="M3">
-        <v>495</v>
+        <v>415</v>
       </c>
       <c r="N3">
-        <v>0.7707489539242163</v>
+        <v>0.001313834503265043</v>
       </c>
       <c r="O3">
-        <v>0.8469582015082</v>
+        <v>4.909452615728609E-05</v>
       </c>
       <c r="P3">
-        <v>-0.6531175255708912</v>
+        <v>0.587817596845857</v>
       </c>
       <c r="Q3">
-        <v>0.04973324219273456</v>
+        <v>3.7259679338161</v>
       </c>
       <c r="R3">
-        <v>0.0007842691076640307</v>
+        <v>-0.0002239271328408037</v>
       </c>
       <c r="S3">
-        <v>0.02621870586511935</v>
+        <v>0.03210615986299115</v>
       </c>
       <c r="T3">
-        <v>194</v>
+        <v>276</v>
       </c>
       <c r="U3">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="V3">
-        <v>0.002095761696200646</v>
+        <v>0.001024022373068393</v>
       </c>
       <c r="W3">
-        <v>0.0002134785454252723</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23">
-      <c r="A4">
-        <v>12</v>
-      </c>
-      <c r="B4">
-        <v>29.44</v>
-      </c>
-      <c r="C4">
-        <v>0.03610792164320767</v>
-      </c>
-      <c r="D4">
-        <v>71.36000000000001</v>
-      </c>
-      <c r="E4">
-        <v>42.72</v>
-      </c>
-      <c r="F4">
-        <v>0.02632605363682696</v>
-      </c>
-      <c r="G4">
-        <v>83.04000000000001</v>
-      </c>
-      <c r="H4">
-        <v>-2.763760255502575</v>
-      </c>
-      <c r="I4">
-        <v>8.150483771559607</v>
-      </c>
-      <c r="J4">
-        <v>0.0009054076366170438</v>
-      </c>
-      <c r="K4">
-        <v>0.04006048965267817</v>
-      </c>
-      <c r="L4">
-        <v>261</v>
-      </c>
-      <c r="M4">
-        <v>445</v>
-      </c>
-      <c r="N4">
-        <v>0.0010938798109798</v>
-      </c>
-      <c r="O4">
-        <v>4.658662661372531E-05</v>
-      </c>
-      <c r="P4">
-        <v>-0.573295102863713</v>
-      </c>
-      <c r="Q4">
-        <v>3.299146976909885</v>
-      </c>
-      <c r="R4">
-        <v>-0.0005611501996359798</v>
-      </c>
-      <c r="S4">
-        <v>0.04546604662594152</v>
-      </c>
-      <c r="T4">
-        <v>251</v>
-      </c>
-      <c r="U4">
-        <v>518</v>
-      </c>
-      <c r="V4">
-        <v>0.000130485229243267</v>
-      </c>
-      <c r="W4">
-        <v>5.18946581741653E-06</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23">
-      <c r="A5">
-        <v>13</v>
-      </c>
-      <c r="B5">
-        <v>130.08</v>
-      </c>
-      <c r="C5">
-        <v>0.002469889499419557</v>
-      </c>
-      <c r="D5">
-        <v>142.24</v>
-      </c>
-      <c r="E5">
-        <v>0.64</v>
-      </c>
-      <c r="F5">
-        <v>0.007744044185880387</v>
-      </c>
-      <c r="G5">
-        <v>2.24</v>
-      </c>
-      <c r="H5">
-        <v>-2.676233833460888</v>
-      </c>
-      <c r="I5">
-        <v>9.324828360135674</v>
-      </c>
-      <c r="J5">
-        <v>-0.001336210726327087</v>
-      </c>
-      <c r="K5">
-        <v>0.01199225032923227</v>
-      </c>
-      <c r="L5">
-        <v>75</v>
-      </c>
-      <c r="M5">
-        <v>888</v>
-      </c>
-      <c r="N5">
-        <v>0.001860642979305037</v>
-      </c>
-      <c r="O5">
-        <v>0.0001060854660824825</v>
-      </c>
-      <c r="P5">
-        <v>0.2833349811658236</v>
-      </c>
-      <c r="Q5">
-        <v>-0.651019863455593</v>
-      </c>
-      <c r="R5">
-        <v>-0.00237870523854025</v>
-      </c>
-      <c r="S5">
-        <v>0.01007664067017811</v>
-      </c>
-      <c r="T5">
-        <v>9</v>
-      </c>
-      <c r="U5">
-        <v>13</v>
-      </c>
-      <c r="V5">
-        <v>0.0324972852338991</v>
-      </c>
-      <c r="W5">
-        <v>0.008193209819591393</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23">
-      <c r="A6">
-        <v>14</v>
-      </c>
-      <c r="B6">
-        <v>71.36000000000001</v>
-      </c>
-      <c r="C6">
-        <v>0.007852700182600307</v>
-      </c>
-      <c r="D6">
-        <v>117.6</v>
-      </c>
-      <c r="E6">
-        <v>43.84</v>
-      </c>
-      <c r="F6">
-        <v>0.02114177073216123</v>
-      </c>
-      <c r="G6">
-        <v>74.72</v>
-      </c>
-      <c r="H6">
-        <v>0.3880093281308312</v>
-      </c>
-      <c r="I6">
-        <v>5.83878369435188</v>
-      </c>
-      <c r="J6">
-        <v>0.000123295968154055</v>
-      </c>
-      <c r="K6">
-        <v>0.01854903067020648</v>
-      </c>
-      <c r="L6">
-        <v>288</v>
-      </c>
-      <c r="M6">
-        <v>734</v>
-      </c>
-      <c r="N6">
-        <v>0.0002536030870855325</v>
-      </c>
-      <c r="O6">
-        <v>1.126256536824595E-06</v>
-      </c>
-      <c r="P6">
-        <v>0.2525813162014702</v>
-      </c>
-      <c r="Q6">
-        <v>1.68975823691552</v>
-      </c>
-      <c r="R6">
-        <v>-0.003164234607174515</v>
-      </c>
-      <c r="S6">
-        <v>0.01721580724241833</v>
-      </c>
-      <c r="T6">
-        <v>192</v>
-      </c>
-      <c r="U6">
-        <v>466</v>
-      </c>
-      <c r="V6">
-        <v>0.001009042593344173</v>
-      </c>
-      <c r="W6">
-        <v>8.264577089035876E-05</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23">
-      <c r="A7">
-        <v>15</v>
-      </c>
-      <c r="B7">
-        <v>60.8</v>
-      </c>
-      <c r="C7">
-        <v>0.008212810720063609</v>
-      </c>
-      <c r="D7">
-        <v>108.16</v>
-      </c>
-      <c r="E7">
-        <v>20.48</v>
-      </c>
-      <c r="F7">
-        <v>0.01353403300712124</v>
-      </c>
-      <c r="G7">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="H7">
-        <v>1.411881921752367</v>
-      </c>
-      <c r="I7">
-        <v>5.345894788971245</v>
-      </c>
-      <c r="J7">
-        <v>0.001338282323900944</v>
-      </c>
-      <c r="K7">
-        <v>0.02677707265779925</v>
-      </c>
-      <c r="L7">
-        <v>295</v>
-      </c>
-      <c r="M7">
-        <v>675</v>
-      </c>
-      <c r="N7">
-        <v>0.0004676391403885697</v>
-      </c>
-      <c r="O7">
-        <v>8.755697705455358E-05</v>
-      </c>
-      <c r="P7">
-        <v>1.615654557059473</v>
-      </c>
-      <c r="Q7">
-        <v>3.510157423571511</v>
-      </c>
-      <c r="R7">
-        <v>-3.765092836702344E-05</v>
-      </c>
-      <c r="S7">
-        <v>0.02596240082470963</v>
-      </c>
-      <c r="T7">
-        <v>311</v>
-      </c>
-      <c r="U7">
-        <v>439</v>
-      </c>
-      <c r="V7">
-        <v>0.0007689221297599104</v>
-      </c>
-      <c r="W7">
-        <v>4.713266552054918E-06</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23">
-      <c r="A8">
-        <v>16</v>
-      </c>
-      <c r="B8">
-        <v>31.36</v>
-      </c>
-      <c r="C8">
-        <v>0.03467166997865731</v>
-      </c>
-      <c r="D8">
-        <v>75.52000000000001</v>
-      </c>
-      <c r="E8">
-        <v>28.8</v>
-      </c>
-      <c r="F8">
-        <v>0.01530785707419493</v>
-      </c>
-      <c r="G8">
-        <v>76.16000000000001</v>
-      </c>
-      <c r="H8">
-        <v>-0.8491643212964515</v>
-      </c>
-      <c r="I8">
-        <v>4.588932797821692</v>
-      </c>
-      <c r="J8">
-        <v>-5.486300570091051E-05</v>
-      </c>
-      <c r="K8">
-        <v>0.03051485408746376</v>
-      </c>
-      <c r="L8">
-        <v>275</v>
-      </c>
-      <c r="M8">
-        <v>471</v>
-      </c>
-      <c r="N8">
-        <v>0.0008991856708976707</v>
-      </c>
-      <c r="O8">
-        <v>9.798959221981582E-05</v>
-      </c>
-      <c r="P8">
-        <v>-1.066599209025287</v>
-      </c>
-      <c r="Q8">
-        <v>2.526693676457811</v>
-      </c>
-      <c r="R8">
-        <v>-0.0003340442893269766</v>
-      </c>
-      <c r="S8">
-        <v>0.02589477159034883</v>
-      </c>
-      <c r="T8">
-        <v>295</v>
-      </c>
-      <c r="U8">
-        <v>475</v>
-      </c>
-      <c r="V8">
-        <v>0.00218978612836585</v>
-      </c>
-      <c r="W8">
-        <v>3.785571543126623E-06</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23">
-      <c r="A9">
-        <v>17</v>
-      </c>
-      <c r="B9">
-        <v>95.68000000000001</v>
-      </c>
-      <c r="C9">
-        <v>0.002617553316373425</v>
-      </c>
-      <c r="D9">
-        <v>135.52</v>
-      </c>
-      <c r="E9">
-        <v>24.64</v>
-      </c>
-      <c r="F9">
-        <v>0.0157436605672381</v>
-      </c>
-      <c r="G9">
-        <v>66.08</v>
-      </c>
-      <c r="H9">
-        <v>-0.8370450237240743</v>
-      </c>
-      <c r="I9">
-        <v>2.902781353520866</v>
-      </c>
-      <c r="J9">
-        <v>0.000113887776867466</v>
-      </c>
-      <c r="K9">
-        <v>0.0150377916880895</v>
-      </c>
-      <c r="L9">
-        <v>248</v>
-      </c>
-      <c r="M9">
-        <v>846</v>
-      </c>
-      <c r="N9">
-        <v>0.0004756831142825025</v>
-      </c>
-      <c r="O9">
-        <v>1.660761501716177E-06</v>
-      </c>
-      <c r="P9">
-        <v>-0.4697787930459011</v>
-      </c>
-      <c r="Q9">
-        <v>1.386860669334919</v>
-      </c>
-      <c r="R9">
-        <v>0.0002831761142650475</v>
-      </c>
-      <c r="S9">
-        <v>0.02996751436151743</v>
-      </c>
-      <c r="T9">
-        <v>258</v>
-      </c>
-      <c r="U9">
-        <v>412</v>
-      </c>
-      <c r="V9">
-        <v>0.0005012384472565072</v>
-      </c>
-      <c r="W9">
-        <v>2.640774999893631E-05</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23">
-      <c r="A10">
-        <v>18</v>
-      </c>
-      <c r="B10">
-        <v>21.12</v>
-      </c>
-      <c r="C10">
-        <v>0.04278861977265875</v>
-      </c>
-      <c r="D10">
-        <v>66.55999999999999</v>
-      </c>
-      <c r="E10">
-        <v>25.28</v>
-      </c>
-      <c r="F10">
-        <v>0.02237448185504321</v>
-      </c>
-      <c r="G10">
-        <v>69.59999999999999</v>
-      </c>
-      <c r="H10">
-        <v>0.2398255713248025</v>
-      </c>
-      <c r="I10">
-        <v>2.977885709940506</v>
-      </c>
-      <c r="J10">
-        <v>-0.0002912686382950547</v>
-      </c>
-      <c r="K10">
-        <v>0.05153352390151887</v>
-      </c>
-      <c r="L10">
-        <v>283</v>
-      </c>
-      <c r="M10">
-        <v>415</v>
-      </c>
-      <c r="N10">
-        <v>0.001313834503265043</v>
-      </c>
-      <c r="O10">
-        <v>4.909452615728609E-05</v>
-      </c>
-      <c r="P10">
-        <v>0.587817596845857</v>
-      </c>
-      <c r="Q10">
-        <v>3.7259679338161</v>
-      </c>
-      <c r="R10">
-        <v>-0.0002239271328408037</v>
-      </c>
-      <c r="S10">
-        <v>0.03210615986299115</v>
-      </c>
-      <c r="T10">
-        <v>276</v>
-      </c>
-      <c r="U10">
-        <v>434</v>
-      </c>
-      <c r="V10">
-        <v>0.001024022373068393</v>
-      </c>
-      <c r="W10">
         <v>7.558357434712283E-06</v>
       </c>
     </row>

--- a/result/xlsx/ecg_analysisresults1.xlsx
+++ b/result/xlsx/ecg_analysisresults1.xlsx
@@ -414,7 +414,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:W4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:23">
@@ -490,143 +490,214 @@
     </row>
     <row r="2" spans="1:23">
       <c r="A2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2">
-        <v>95.68000000000001</v>
+        <v>31.36</v>
       </c>
       <c r="C2">
-        <v>0.002617553316373425</v>
+        <v>0.03467166997865731</v>
       </c>
       <c r="D2">
-        <v>135.52</v>
+        <v>75.52000000000001</v>
       </c>
       <c r="E2">
-        <v>24.64</v>
+        <v>28.8</v>
       </c>
       <c r="F2">
-        <v>0.0157436605672381</v>
+        <v>0.01530785707419493</v>
       </c>
       <c r="G2">
-        <v>66.08</v>
+        <v>76.16000000000001</v>
       </c>
       <c r="H2">
-        <v>-0.8370450237240743</v>
+        <v>-0.8491643212964515</v>
       </c>
       <c r="I2">
-        <v>2.902781353520866</v>
+        <v>4.588932797821692</v>
       </c>
       <c r="J2">
-        <v>0.000113887776867466</v>
+        <v>-5.486300570091051E-05</v>
       </c>
       <c r="K2">
-        <v>0.0150377916880895</v>
+        <v>0.03051485408746376</v>
       </c>
       <c r="L2">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c r="M2">
-        <v>846</v>
+        <v>471</v>
       </c>
       <c r="N2">
-        <v>0.0004756831142825025</v>
+        <v>0.0008991856708976707</v>
       </c>
       <c r="O2">
-        <v>1.660761501716177E-06</v>
+        <v>9.798959221981582E-05</v>
       </c>
       <c r="P2">
-        <v>-0.4697787930459011</v>
+        <v>-1.066599209025287</v>
       </c>
       <c r="Q2">
-        <v>1.386860669334919</v>
+        <v>2.526693676457811</v>
       </c>
       <c r="R2">
-        <v>0.0002831761142650475</v>
+        <v>-0.0003340442893269766</v>
       </c>
       <c r="S2">
-        <v>0.02996751436151743</v>
+        <v>0.02589477159034883</v>
       </c>
       <c r="T2">
-        <v>258</v>
+        <v>295</v>
       </c>
       <c r="U2">
-        <v>412</v>
+        <v>475</v>
       </c>
       <c r="V2">
-        <v>0.0005012384472565072</v>
+        <v>0.00218978612836585</v>
       </c>
       <c r="W2">
-        <v>2.640774999893631E-05</v>
+        <v>3.785571543126623E-06</v>
       </c>
     </row>
     <row r="3" spans="1:23">
       <c r="A3">
+        <v>17</v>
+      </c>
+      <c r="B3">
+        <v>95.68000000000001</v>
+      </c>
+      <c r="C3">
+        <v>0.002617553316373425</v>
+      </c>
+      <c r="D3">
+        <v>135.52</v>
+      </c>
+      <c r="E3">
+        <v>24.64</v>
+      </c>
+      <c r="F3">
+        <v>0.0157436605672381</v>
+      </c>
+      <c r="G3">
+        <v>66.08</v>
+      </c>
+      <c r="H3">
+        <v>-0.8370450237240743</v>
+      </c>
+      <c r="I3">
+        <v>2.902781353520866</v>
+      </c>
+      <c r="J3">
+        <v>0.000113887776867466</v>
+      </c>
+      <c r="K3">
+        <v>0.0150377916880895</v>
+      </c>
+      <c r="L3">
+        <v>248</v>
+      </c>
+      <c r="M3">
+        <v>846</v>
+      </c>
+      <c r="N3">
+        <v>0.0004756831142825025</v>
+      </c>
+      <c r="O3">
+        <v>1.660761501716177E-06</v>
+      </c>
+      <c r="P3">
+        <v>-0.4697787930459011</v>
+      </c>
+      <c r="Q3">
+        <v>1.386860669334919</v>
+      </c>
+      <c r="R3">
+        <v>0.0002831761142650475</v>
+      </c>
+      <c r="S3">
+        <v>0.02996751436151743</v>
+      </c>
+      <c r="T3">
+        <v>258</v>
+      </c>
+      <c r="U3">
+        <v>412</v>
+      </c>
+      <c r="V3">
+        <v>0.0005012384472565072</v>
+      </c>
+      <c r="W3">
+        <v>2.640774999893631E-05</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23">
+      <c r="A4">
         <v>18</v>
       </c>
-      <c r="B3">
+      <c r="B4">
         <v>21.12</v>
       </c>
-      <c r="C3">
+      <c r="C4">
         <v>0.04278861977265875</v>
       </c>
-      <c r="D3">
+      <c r="D4">
         <v>66.55999999999999</v>
       </c>
-      <c r="E3">
+      <c r="E4">
         <v>25.28</v>
       </c>
-      <c r="F3">
+      <c r="F4">
         <v>0.02237448185504321</v>
       </c>
-      <c r="G3">
+      <c r="G4">
         <v>69.59999999999999</v>
       </c>
-      <c r="H3">
+      <c r="H4">
         <v>0.2398255713248025</v>
       </c>
-      <c r="I3">
+      <c r="I4">
         <v>2.977885709940506</v>
       </c>
-      <c r="J3">
+      <c r="J4">
         <v>-0.0002912686382950547</v>
       </c>
-      <c r="K3">
+      <c r="K4">
         <v>0.05153352390151887</v>
       </c>
-      <c r="L3">
+      <c r="L4">
         <v>283</v>
       </c>
-      <c r="M3">
+      <c r="M4">
         <v>415</v>
       </c>
-      <c r="N3">
+      <c r="N4">
         <v>0.001313834503265043</v>
       </c>
-      <c r="O3">
+      <c r="O4">
         <v>4.909452615728609E-05</v>
       </c>
-      <c r="P3">
+      <c r="P4">
         <v>0.587817596845857</v>
       </c>
-      <c r="Q3">
+      <c r="Q4">
         <v>3.7259679338161</v>
       </c>
-      <c r="R3">
+      <c r="R4">
         <v>-0.0002239271328408037</v>
       </c>
-      <c r="S3">
+      <c r="S4">
         <v>0.03210615986299115</v>
       </c>
-      <c r="T3">
+      <c r="T4">
         <v>276</v>
       </c>
-      <c r="U3">
+      <c r="U4">
         <v>434</v>
       </c>
-      <c r="V3">
+      <c r="V4">
         <v>0.001024022373068393</v>
       </c>
-      <c r="W3">
+      <c r="W4">
         <v>7.558357434712283E-06</v>
       </c>
     </row>

--- a/result/xlsx/ecg_analysisresults1.xlsx
+++ b/result/xlsx/ecg_analysisresults1.xlsx
@@ -414,7 +414,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W4"/>
+  <dimension ref="A1:W10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:23">
@@ -490,214 +490,640 @@
     </row>
     <row r="2" spans="1:23">
       <c r="A2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B2">
-        <v>31.36</v>
+        <v>33.92</v>
       </c>
       <c r="C2">
-        <v>0.03467166997865731</v>
+        <v>0.03933095212484044</v>
       </c>
       <c r="D2">
-        <v>75.52000000000001</v>
+        <v>79.36</v>
       </c>
       <c r="E2">
-        <v>28.8</v>
+        <v>26.08</v>
       </c>
       <c r="F2">
-        <v>0.01530785707419493</v>
+        <v>0.01289097725725355</v>
       </c>
       <c r="G2">
-        <v>76.16000000000001</v>
+        <v>70.88</v>
       </c>
       <c r="H2">
-        <v>-0.8491643212964515</v>
+        <v>-2.896416525808391</v>
       </c>
       <c r="I2">
-        <v>4.588932797821692</v>
+        <v>9.680644607493234</v>
       </c>
       <c r="J2">
-        <v>-5.486300570091051E-05</v>
+        <v>-0.0004792050467676656</v>
       </c>
       <c r="K2">
-        <v>0.03051485408746376</v>
+        <v>0.0451034416093991</v>
       </c>
       <c r="L2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="M2">
-        <v>471</v>
+        <v>495</v>
       </c>
       <c r="N2">
-        <v>0.0008991856708976707</v>
+        <v>0.00106316628233838</v>
       </c>
       <c r="O2">
-        <v>9.798959221981582E-05</v>
+        <v>7.401774184589742E-05</v>
       </c>
       <c r="P2">
-        <v>-1.066599209025287</v>
+        <v>-0.9938436486225042</v>
       </c>
       <c r="Q2">
-        <v>2.526693676457811</v>
+        <v>2.252580888018167</v>
       </c>
       <c r="R2">
-        <v>-0.0003340442893269766</v>
+        <v>-0.001712533510177653</v>
       </c>
       <c r="S2">
-        <v>0.02589477159034883</v>
+        <v>0.02942047582720344</v>
       </c>
       <c r="T2">
-        <v>295</v>
+        <v>279</v>
       </c>
       <c r="U2">
-        <v>475</v>
+        <v>442</v>
       </c>
       <c r="V2">
-        <v>0.00218978612836585</v>
+        <v>0.002233622324148771</v>
       </c>
       <c r="W2">
-        <v>3.785571543126623E-06</v>
+        <v>7.949197975276071E-07</v>
       </c>
     </row>
     <row r="3" spans="1:23">
       <c r="A3">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B3">
-        <v>95.68000000000001</v>
+        <v>33.92</v>
       </c>
       <c r="C3">
-        <v>0.002617553316373425</v>
+        <v>0.03933095212484044</v>
       </c>
       <c r="D3">
-        <v>135.52</v>
+        <v>79.36</v>
       </c>
       <c r="E3">
-        <v>24.64</v>
+        <v>31.84</v>
       </c>
       <c r="F3">
-        <v>0.0157436605672381</v>
+        <v>0.01545207381696054</v>
       </c>
       <c r="G3">
-        <v>66.08</v>
+        <v>63.04</v>
       </c>
       <c r="H3">
-        <v>-0.8370450237240743</v>
+        <v>0.1709219072410759</v>
       </c>
       <c r="I3">
-        <v>2.902781353520866</v>
+        <v>8.435502017955752</v>
       </c>
       <c r="J3">
-        <v>0.000113887776867466</v>
+        <v>6.012526834551568E-06</v>
       </c>
       <c r="K3">
-        <v>0.0150377916880895</v>
+        <v>0.00306136076858581</v>
       </c>
       <c r="L3">
-        <v>248</v>
+        <v>283</v>
       </c>
       <c r="M3">
-        <v>846</v>
+        <v>495</v>
       </c>
       <c r="N3">
-        <v>0.0004756831142825025</v>
+        <v>0.7707489539242163</v>
       </c>
       <c r="O3">
-        <v>1.660761501716177E-06</v>
+        <v>0.8469582015082</v>
       </c>
       <c r="P3">
-        <v>-0.4697787930459011</v>
+        <v>-0.6531175255708912</v>
       </c>
       <c r="Q3">
-        <v>1.386860669334919</v>
+        <v>0.04973324219273456</v>
       </c>
       <c r="R3">
-        <v>0.0002831761142650475</v>
+        <v>0.0007842691076640307</v>
       </c>
       <c r="S3">
-        <v>0.02996751436151743</v>
+        <v>0.02621870586511935</v>
       </c>
       <c r="T3">
-        <v>258</v>
+        <v>194</v>
       </c>
       <c r="U3">
-        <v>412</v>
+        <v>393</v>
       </c>
       <c r="V3">
-        <v>0.0005012384472565072</v>
+        <v>0.002095761696200646</v>
       </c>
       <c r="W3">
-        <v>2.640774999893631E-05</v>
+        <v>0.0002134785454252723</v>
       </c>
     </row>
     <row r="4" spans="1:23">
       <c r="A4">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>29.44</v>
+      </c>
+      <c r="C4">
+        <v>0.03610792164320767</v>
+      </c>
+      <c r="D4">
+        <v>71.36000000000001</v>
+      </c>
+      <c r="E4">
+        <v>42.72</v>
+      </c>
+      <c r="F4">
+        <v>0.02632605363682696</v>
+      </c>
+      <c r="G4">
+        <v>83.04000000000001</v>
+      </c>
+      <c r="H4">
+        <v>-2.763760255502575</v>
+      </c>
+      <c r="I4">
+        <v>8.150483771559607</v>
+      </c>
+      <c r="J4">
+        <v>0.0009054076366170438</v>
+      </c>
+      <c r="K4">
+        <v>0.04006048965267817</v>
+      </c>
+      <c r="L4">
+        <v>261</v>
+      </c>
+      <c r="M4">
+        <v>445</v>
+      </c>
+      <c r="N4">
+        <v>0.0010938798109798</v>
+      </c>
+      <c r="O4">
+        <v>4.658662661372531E-05</v>
+      </c>
+      <c r="P4">
+        <v>-0.573295102863713</v>
+      </c>
+      <c r="Q4">
+        <v>3.299146976909885</v>
+      </c>
+      <c r="R4">
+        <v>-0.0005611501996359798</v>
+      </c>
+      <c r="S4">
+        <v>0.04546604662594152</v>
+      </c>
+      <c r="T4">
+        <v>251</v>
+      </c>
+      <c r="U4">
+        <v>518</v>
+      </c>
+      <c r="V4">
+        <v>0.000130485229243267</v>
+      </c>
+      <c r="W4">
+        <v>5.18946581741653E-06</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23">
+      <c r="A5">
+        <v>13</v>
+      </c>
+      <c r="B5">
+        <v>130.08</v>
+      </c>
+      <c r="C5">
+        <v>0.002469889499419557</v>
+      </c>
+      <c r="D5">
+        <v>142.24</v>
+      </c>
+      <c r="E5">
+        <v>0.64</v>
+      </c>
+      <c r="F5">
+        <v>0.007744044185880387</v>
+      </c>
+      <c r="G5">
+        <v>2.24</v>
+      </c>
+      <c r="H5">
+        <v>-2.676233833460888</v>
+      </c>
+      <c r="I5">
+        <v>9.324828360135674</v>
+      </c>
+      <c r="J5">
+        <v>-0.001336210726327087</v>
+      </c>
+      <c r="K5">
+        <v>0.01199225032923227</v>
+      </c>
+      <c r="L5">
+        <v>75</v>
+      </c>
+      <c r="M5">
+        <v>888</v>
+      </c>
+      <c r="N5">
+        <v>0.001860642979305037</v>
+      </c>
+      <c r="O5">
+        <v>0.0001060854660824825</v>
+      </c>
+      <c r="P5">
+        <v>0.2833349811658236</v>
+      </c>
+      <c r="Q5">
+        <v>-0.651019863455593</v>
+      </c>
+      <c r="R5">
+        <v>-0.00237870523854025</v>
+      </c>
+      <c r="S5">
+        <v>0.01007664067017811</v>
+      </c>
+      <c r="T5">
+        <v>9</v>
+      </c>
+      <c r="U5">
+        <v>13</v>
+      </c>
+      <c r="V5">
+        <v>0.0324972852338991</v>
+      </c>
+      <c r="W5">
+        <v>0.008193209819591393</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23">
+      <c r="A6">
+        <v>14</v>
+      </c>
+      <c r="B6">
+        <v>71.36000000000001</v>
+      </c>
+      <c r="C6">
+        <v>0.007852700182600307</v>
+      </c>
+      <c r="D6">
+        <v>117.6</v>
+      </c>
+      <c r="E6">
+        <v>43.84</v>
+      </c>
+      <c r="F6">
+        <v>0.02114177073216123</v>
+      </c>
+      <c r="G6">
+        <v>74.72</v>
+      </c>
+      <c r="H6">
+        <v>0.3880093281308312</v>
+      </c>
+      <c r="I6">
+        <v>5.83878369435188</v>
+      </c>
+      <c r="J6">
+        <v>0.000123295968154055</v>
+      </c>
+      <c r="K6">
+        <v>0.01854903067020648</v>
+      </c>
+      <c r="L6">
+        <v>288</v>
+      </c>
+      <c r="M6">
+        <v>734</v>
+      </c>
+      <c r="N6">
+        <v>0.0002536030870855325</v>
+      </c>
+      <c r="O6">
+        <v>1.126256536824595E-06</v>
+      </c>
+      <c r="P6">
+        <v>0.2525813162014702</v>
+      </c>
+      <c r="Q6">
+        <v>1.68975823691552</v>
+      </c>
+      <c r="R6">
+        <v>-0.003164234607174515</v>
+      </c>
+      <c r="S6">
+        <v>0.01721580724241833</v>
+      </c>
+      <c r="T6">
+        <v>192</v>
+      </c>
+      <c r="U6">
+        <v>466</v>
+      </c>
+      <c r="V6">
+        <v>0.001009042593344173</v>
+      </c>
+      <c r="W6">
+        <v>8.264577089035876E-05</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23">
+      <c r="A7">
+        <v>15</v>
+      </c>
+      <c r="B7">
+        <v>60.8</v>
+      </c>
+      <c r="C7">
+        <v>0.008212810720063609</v>
+      </c>
+      <c r="D7">
+        <v>108.16</v>
+      </c>
+      <c r="E7">
+        <v>20.48</v>
+      </c>
+      <c r="F7">
+        <v>0.01353403300712124</v>
+      </c>
+      <c r="G7">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="H7">
+        <v>1.411881921752367</v>
+      </c>
+      <c r="I7">
+        <v>5.345894788971245</v>
+      </c>
+      <c r="J7">
+        <v>0.001338282323900944</v>
+      </c>
+      <c r="K7">
+        <v>0.02677707265779925</v>
+      </c>
+      <c r="L7">
+        <v>295</v>
+      </c>
+      <c r="M7">
+        <v>675</v>
+      </c>
+      <c r="N7">
+        <v>0.0004676391403885697</v>
+      </c>
+      <c r="O7">
+        <v>8.755697705455358E-05</v>
+      </c>
+      <c r="P7">
+        <v>1.615654557059473</v>
+      </c>
+      <c r="Q7">
+        <v>3.510157423571511</v>
+      </c>
+      <c r="R7">
+        <v>-3.765092836702344E-05</v>
+      </c>
+      <c r="S7">
+        <v>0.02596240082470963</v>
+      </c>
+      <c r="T7">
+        <v>311</v>
+      </c>
+      <c r="U7">
+        <v>439</v>
+      </c>
+      <c r="V7">
+        <v>0.0007689221297599104</v>
+      </c>
+      <c r="W7">
+        <v>4.713266552054918E-06</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23">
+      <c r="A8">
+        <v>16</v>
+      </c>
+      <c r="B8">
+        <v>31.36</v>
+      </c>
+      <c r="C8">
+        <v>0.03467166997865731</v>
+      </c>
+      <c r="D8">
+        <v>75.52000000000001</v>
+      </c>
+      <c r="E8">
+        <v>28.8</v>
+      </c>
+      <c r="F8">
+        <v>0.01530785707419493</v>
+      </c>
+      <c r="G8">
+        <v>76.16000000000001</v>
+      </c>
+      <c r="H8">
+        <v>-0.8491643212964515</v>
+      </c>
+      <c r="I8">
+        <v>4.588932797821692</v>
+      </c>
+      <c r="J8">
+        <v>-5.486300570091051E-05</v>
+      </c>
+      <c r="K8">
+        <v>0.03051485408746376</v>
+      </c>
+      <c r="L8">
+        <v>275</v>
+      </c>
+      <c r="M8">
+        <v>471</v>
+      </c>
+      <c r="N8">
+        <v>0.0008991856708976707</v>
+      </c>
+      <c r="O8">
+        <v>9.798959221981582E-05</v>
+      </c>
+      <c r="P8">
+        <v>-1.066599209025287</v>
+      </c>
+      <c r="Q8">
+        <v>2.526693676457811</v>
+      </c>
+      <c r="R8">
+        <v>-0.0003340442893269766</v>
+      </c>
+      <c r="S8">
+        <v>0.02589477159034883</v>
+      </c>
+      <c r="T8">
+        <v>295</v>
+      </c>
+      <c r="U8">
+        <v>475</v>
+      </c>
+      <c r="V8">
+        <v>0.00218978612836585</v>
+      </c>
+      <c r="W8">
+        <v>3.785571543126623E-06</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23">
+      <c r="A9">
+        <v>17</v>
+      </c>
+      <c r="B9">
+        <v>95.68000000000001</v>
+      </c>
+      <c r="C9">
+        <v>0.002617553316373425</v>
+      </c>
+      <c r="D9">
+        <v>135.52</v>
+      </c>
+      <c r="E9">
+        <v>24.64</v>
+      </c>
+      <c r="F9">
+        <v>0.0157436605672381</v>
+      </c>
+      <c r="G9">
+        <v>66.08</v>
+      </c>
+      <c r="H9">
+        <v>-0.8370450237240743</v>
+      </c>
+      <c r="I9">
+        <v>2.902781353520866</v>
+      </c>
+      <c r="J9">
+        <v>0.000113887776867466</v>
+      </c>
+      <c r="K9">
+        <v>0.0150377916880895</v>
+      </c>
+      <c r="L9">
+        <v>248</v>
+      </c>
+      <c r="M9">
+        <v>846</v>
+      </c>
+      <c r="N9">
+        <v>0.0004756831142825025</v>
+      </c>
+      <c r="O9">
+        <v>1.660761501716177E-06</v>
+      </c>
+      <c r="P9">
+        <v>-0.4697787930459011</v>
+      </c>
+      <c r="Q9">
+        <v>1.386860669334919</v>
+      </c>
+      <c r="R9">
+        <v>0.0002831761142650475</v>
+      </c>
+      <c r="S9">
+        <v>0.02996751436151743</v>
+      </c>
+      <c r="T9">
+        <v>258</v>
+      </c>
+      <c r="U9">
+        <v>412</v>
+      </c>
+      <c r="V9">
+        <v>0.0005012384472565072</v>
+      </c>
+      <c r="W9">
+        <v>2.640774999893631E-05</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23">
+      <c r="A10">
         <v>18</v>
       </c>
-      <c r="B4">
+      <c r="B10">
         <v>21.12</v>
       </c>
-      <c r="C4">
+      <c r="C10">
         <v>0.04278861977265875</v>
       </c>
-      <c r="D4">
+      <c r="D10">
         <v>66.55999999999999</v>
       </c>
-      <c r="E4">
+      <c r="E10">
         <v>25.28</v>
       </c>
-      <c r="F4">
+      <c r="F10">
         <v>0.02237448185504321</v>
       </c>
-      <c r="G4">
+      <c r="G10">
         <v>69.59999999999999</v>
       </c>
-      <c r="H4">
+      <c r="H10">
         <v>0.2398255713248025</v>
       </c>
-      <c r="I4">
+      <c r="I10">
         <v>2.977885709940506</v>
       </c>
-      <c r="J4">
+      <c r="J10">
         <v>-0.0002912686382950547</v>
       </c>
-      <c r="K4">
+      <c r="K10">
         <v>0.05153352390151887</v>
       </c>
-      <c r="L4">
+      <c r="L10">
         <v>283</v>
       </c>
-      <c r="M4">
+      <c r="M10">
         <v>415</v>
       </c>
-      <c r="N4">
+      <c r="N10">
         <v>0.001313834503265043</v>
       </c>
-      <c r="O4">
+      <c r="O10">
         <v>4.909452615728609E-05</v>
       </c>
-      <c r="P4">
+      <c r="P10">
         <v>0.587817596845857</v>
       </c>
-      <c r="Q4">
+      <c r="Q10">
         <v>3.7259679338161</v>
       </c>
-      <c r="R4">
+      <c r="R10">
         <v>-0.0002239271328408037</v>
       </c>
-      <c r="S4">
+      <c r="S10">
         <v>0.03210615986299115</v>
       </c>
-      <c r="T4">
+      <c r="T10">
         <v>276</v>
       </c>
-      <c r="U4">
+      <c r="U10">
         <v>434</v>
       </c>
-      <c r="V4">
+      <c r="V10">
         <v>0.001024022373068393</v>
       </c>
-      <c r="W4">
+      <c r="W10">
         <v>7.558357434712283E-06</v>
       </c>
     </row>

--- a/result/xlsx/ecg_analysisresults1.xlsx
+++ b/result/xlsx/ecg_analysisresults1.xlsx
@@ -493,70 +493,70 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>33.92</v>
+        <v>34.24</v>
       </c>
       <c r="C2">
-        <v>0.03933095212484044</v>
+        <v>0.03989002784726506</v>
       </c>
       <c r="D2">
-        <v>79.36</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="E2">
-        <v>26.08</v>
+        <v>26.72</v>
       </c>
       <c r="F2">
-        <v>0.01289097725725355</v>
+        <v>0.01320625744209405</v>
       </c>
       <c r="G2">
-        <v>70.88</v>
+        <v>71.36000000000001</v>
       </c>
       <c r="H2">
-        <v>-2.896416525808391</v>
+        <v>-2.91799720136641</v>
       </c>
       <c r="I2">
-        <v>9.680644607493234</v>
+        <v>9.487728105939796</v>
       </c>
       <c r="J2">
-        <v>-0.0004792050467676656</v>
+        <v>-0.000565788861687424</v>
       </c>
       <c r="K2">
-        <v>0.0451034416093991</v>
+        <v>0.04637570178724547</v>
       </c>
       <c r="L2">
         <v>283</v>
       </c>
       <c r="M2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="N2">
-        <v>0.00106316628233838</v>
+        <v>0.001388430588468457</v>
       </c>
       <c r="O2">
-        <v>7.401774184589742E-05</v>
+        <v>8.439569881246977E-05</v>
       </c>
       <c r="P2">
-        <v>-0.9938436486225042</v>
+        <v>-1.097062782219975</v>
       </c>
       <c r="Q2">
-        <v>2.252580888018167</v>
+        <v>2.537530552679585</v>
       </c>
       <c r="R2">
-        <v>-0.001712533510177653</v>
+        <v>-0.001828023599046852</v>
       </c>
       <c r="S2">
-        <v>0.02942047582720344</v>
+        <v>0.02851497604107792</v>
       </c>
       <c r="T2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="U2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="V2">
-        <v>0.002233622324148771</v>
+        <v>0.001911950034725556</v>
       </c>
       <c r="W2">
-        <v>7.949197975276071E-07</v>
+        <v>2.061278578795905E-06</v>
       </c>
     </row>
     <row r="3" spans="1:23">
@@ -564,70 +564,70 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>33.92</v>
+        <v>80</v>
       </c>
       <c r="C3">
-        <v>0.03933095212484044</v>
+        <v>0.0005009595324494126</v>
       </c>
       <c r="D3">
-        <v>79.36</v>
+        <v>150.24</v>
       </c>
       <c r="E3">
-        <v>31.84</v>
+        <v>33.76</v>
       </c>
       <c r="F3">
-        <v>0.01545207381696054</v>
+        <v>0.01732683839407854</v>
       </c>
       <c r="G3">
-        <v>63.04</v>
+        <v>64.8</v>
       </c>
       <c r="H3">
-        <v>0.1709219072410759</v>
+        <v>-0.005034429458719266</v>
       </c>
       <c r="I3">
-        <v>8.435502017955752</v>
+        <v>8.819301343365815</v>
       </c>
       <c r="J3">
-        <v>6.012526834551568E-06</v>
+        <v>1.308879340764767E-05</v>
       </c>
       <c r="K3">
-        <v>0.00306136076858581</v>
+        <v>0.002886567095355565</v>
       </c>
       <c r="L3">
-        <v>283</v>
+        <v>438</v>
       </c>
       <c r="M3">
-        <v>495</v>
+        <v>938</v>
       </c>
       <c r="N3">
-        <v>0.7707489539242163</v>
+        <v>0.7782237877830444</v>
       </c>
       <c r="O3">
-        <v>0.8469582015082</v>
+        <v>0.8575770384199922</v>
       </c>
       <c r="P3">
-        <v>-0.6531175255708912</v>
+        <v>-1.064347071408852</v>
       </c>
       <c r="Q3">
-        <v>0.04973324219273456</v>
+        <v>0.1642435992607978</v>
       </c>
       <c r="R3">
-        <v>0.0007842691076640307</v>
+        <v>0.0008846246880419261</v>
       </c>
       <c r="S3">
-        <v>0.02621870586511935</v>
+        <v>0.0306158876993277</v>
       </c>
       <c r="T3">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="U3">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="V3">
-        <v>0.002095761696200646</v>
+        <v>0.003166355859813709</v>
       </c>
       <c r="W3">
-        <v>0.0002134785454252723</v>
+        <v>0.0002132957029321773</v>
       </c>
     </row>
     <row r="4" spans="1:23">
@@ -635,70 +635,70 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>29.44</v>
+        <v>29.76</v>
       </c>
       <c r="C4">
-        <v>0.03610792164320767</v>
+        <v>0.03663689475000673</v>
       </c>
       <c r="D4">
         <v>71.36000000000001</v>
       </c>
       <c r="E4">
-        <v>42.72</v>
+        <v>73.92</v>
       </c>
       <c r="F4">
-        <v>0.02632605363682696</v>
+        <v>0.02935096252591826</v>
       </c>
       <c r="G4">
-        <v>83.04000000000001</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="H4">
-        <v>-2.763760255502575</v>
+        <v>-2.749823940923068</v>
       </c>
       <c r="I4">
-        <v>8.150483771559607</v>
+        <v>7.989515616789749</v>
       </c>
       <c r="J4">
-        <v>0.0009054076366170438</v>
+        <v>0.0008878245845468591</v>
       </c>
       <c r="K4">
-        <v>0.04006048965267817</v>
+        <v>0.04102558351112833</v>
       </c>
       <c r="L4">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="M4">
         <v>445</v>
       </c>
       <c r="N4">
-        <v>0.0010938798109798</v>
+        <v>0.001144086673244057</v>
       </c>
       <c r="O4">
-        <v>4.658662661372531E-05</v>
+        <v>6.636005579377209E-05</v>
       </c>
       <c r="P4">
-        <v>-0.573295102863713</v>
+        <v>-0.6067122499398648</v>
       </c>
       <c r="Q4">
-        <v>3.299146976909885</v>
+        <v>2.812309923944136</v>
       </c>
       <c r="R4">
-        <v>-0.0005611501996359798</v>
+        <v>-7.812630022722455E-05</v>
       </c>
       <c r="S4">
-        <v>0.04546604662594152</v>
+        <v>0.0529306722201914</v>
       </c>
       <c r="T4">
-        <v>251</v>
+        <v>60</v>
       </c>
       <c r="U4">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="V4">
-        <v>0.000130485229243267</v>
+        <v>0.000153868265623586</v>
       </c>
       <c r="W4">
-        <v>5.18946581741653E-06</v>
+        <v>6.330004307736059E-06</v>
       </c>
     </row>
     <row r="5" spans="1:23">
@@ -706,70 +706,70 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>130.08</v>
+        <v>129.28</v>
       </c>
       <c r="C5">
-        <v>0.002469889499419557</v>
+        <v>0.002805363799071066</v>
       </c>
       <c r="D5">
-        <v>142.24</v>
+        <v>141.44</v>
       </c>
       <c r="E5">
-        <v>0.64</v>
+        <v>53.92</v>
       </c>
       <c r="F5">
-        <v>0.007744044185880387</v>
+        <v>0.003760057799617352</v>
       </c>
       <c r="G5">
-        <v>2.24</v>
+        <v>60.48</v>
       </c>
       <c r="H5">
-        <v>-2.676233833460888</v>
+        <v>-2.516457918257631</v>
       </c>
       <c r="I5">
-        <v>9.324828360135674</v>
+        <v>8.348747943815287</v>
       </c>
       <c r="J5">
-        <v>-0.001336210726327087</v>
+        <v>-0.0004989709587610644</v>
       </c>
       <c r="K5">
-        <v>0.01199225032923227</v>
+        <v>0.01072514995941691</v>
       </c>
       <c r="L5">
         <v>75</v>
       </c>
       <c r="M5">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="N5">
-        <v>0.001860642979305037</v>
+        <v>0.001692661056668869</v>
       </c>
       <c r="O5">
-        <v>0.0001060854660824825</v>
+        <v>0.0001166074689409999</v>
       </c>
       <c r="P5">
-        <v>0.2833349811658236</v>
+        <v>-0.4848049280043791</v>
       </c>
       <c r="Q5">
-        <v>-0.651019863455593</v>
+        <v>-0.1210025901395269</v>
       </c>
       <c r="R5">
-        <v>-0.00237870523854025</v>
+        <v>-0.003246669872144651</v>
       </c>
       <c r="S5">
-        <v>0.01007664067017811</v>
+        <v>0.00979892514100046</v>
       </c>
       <c r="T5">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="U5">
-        <v>13</v>
+        <v>377</v>
       </c>
       <c r="V5">
-        <v>0.0324972852338991</v>
+        <v>0.04492601689670915</v>
       </c>
       <c r="W5">
-        <v>0.008193209819591393</v>
+        <v>0.01212145719598905</v>
       </c>
     </row>
     <row r="6" spans="1:23">
@@ -777,70 +777,70 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>71.36000000000001</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="C6">
-        <v>0.007852700182600307</v>
+        <v>0.004980976642308281</v>
       </c>
       <c r="D6">
-        <v>117.6</v>
+        <v>116</v>
       </c>
       <c r="E6">
-        <v>43.84</v>
+        <v>37.92</v>
       </c>
       <c r="F6">
-        <v>0.02114177073216123</v>
+        <v>0.02683053185920529</v>
       </c>
       <c r="G6">
-        <v>74.72</v>
+        <v>82.55999999999999</v>
       </c>
       <c r="H6">
-        <v>0.3880093281308312</v>
+        <v>0.2101468050660911</v>
       </c>
       <c r="I6">
-        <v>5.83878369435188</v>
+        <v>7.187757737805665</v>
       </c>
       <c r="J6">
-        <v>0.000123295968154055</v>
+        <v>-0.0001473155206192475</v>
       </c>
       <c r="K6">
-        <v>0.01854903067020648</v>
+        <v>0.02068638057084663</v>
       </c>
       <c r="L6">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="M6">
-        <v>734</v>
+        <v>724</v>
       </c>
       <c r="N6">
-        <v>0.0002536030870855325</v>
+        <v>0.000443411054498282</v>
       </c>
       <c r="O6">
-        <v>1.126256536824595E-06</v>
+        <v>2.575906305306628E-05</v>
       </c>
       <c r="P6">
-        <v>0.2525813162014702</v>
+        <v>1.646837224725429</v>
       </c>
       <c r="Q6">
-        <v>1.68975823691552</v>
+        <v>5.96785241765285</v>
       </c>
       <c r="R6">
-        <v>-0.003164234607174515</v>
+        <v>-0.003146103464003431</v>
       </c>
       <c r="S6">
-        <v>0.01721580724241833</v>
+        <v>0.0257236863352771</v>
       </c>
       <c r="T6">
-        <v>192</v>
+        <v>278</v>
       </c>
       <c r="U6">
-        <v>466</v>
+        <v>515</v>
       </c>
       <c r="V6">
-        <v>0.001009042593344173</v>
+        <v>0.0009788215948251305</v>
       </c>
       <c r="W6">
-        <v>8.264577089035876E-05</v>
+        <v>8.511598585391653E-05</v>
       </c>
     </row>
     <row r="7" spans="1:23">
@@ -848,70 +848,70 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>60.8</v>
+        <v>21.44</v>
       </c>
       <c r="C7">
-        <v>0.008212810720063609</v>
+        <v>0.02952097900191285</v>
       </c>
       <c r="D7">
-        <v>108.16</v>
+        <v>68.48</v>
       </c>
       <c r="E7">
-        <v>20.48</v>
+        <v>20.32</v>
       </c>
       <c r="F7">
-        <v>0.01353403300712124</v>
+        <v>0.0126930232920698</v>
       </c>
       <c r="G7">
-        <v>70.40000000000001</v>
+        <v>70.56</v>
       </c>
       <c r="H7">
-        <v>1.411881921752367</v>
+        <v>1.328375859320212</v>
       </c>
       <c r="I7">
-        <v>5.345894788971245</v>
+        <v>5.37088628167027</v>
       </c>
       <c r="J7">
-        <v>0.001338282323900944</v>
+        <v>0.0009273769980443077</v>
       </c>
       <c r="K7">
-        <v>0.02677707265779925</v>
+        <v>0.02839640640096549</v>
       </c>
       <c r="L7">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="M7">
-        <v>675</v>
+        <v>427</v>
       </c>
       <c r="N7">
-        <v>0.0004676391403885697</v>
+        <v>0.0005295930856930405</v>
       </c>
       <c r="O7">
-        <v>8.755697705455358E-05</v>
+        <v>9.052913858930483E-05</v>
       </c>
       <c r="P7">
-        <v>1.615654557059473</v>
+        <v>1.523179775703952</v>
       </c>
       <c r="Q7">
-        <v>3.510157423571511</v>
+        <v>3.0360354400704</v>
       </c>
       <c r="R7">
-        <v>-3.765092836702344E-05</v>
+        <v>2.671344715279744E-06</v>
       </c>
       <c r="S7">
-        <v>0.02596240082470963</v>
+        <v>0.02708157738562428</v>
       </c>
       <c r="T7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="U7">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="V7">
-        <v>0.0007689221297599104</v>
+        <v>0.001332709963639083</v>
       </c>
       <c r="W7">
-        <v>4.713266552054918E-06</v>
+        <v>4.439594164369012E-06</v>
       </c>
     </row>
     <row r="8" spans="1:23">
@@ -919,70 +919,70 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>31.36</v>
+        <v>30.88</v>
       </c>
       <c r="C8">
-        <v>0.03467166997865731</v>
+        <v>0.03406822058128589</v>
       </c>
       <c r="D8">
-        <v>75.52000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="E8">
-        <v>28.8</v>
+        <v>40.64</v>
       </c>
       <c r="F8">
-        <v>0.01530785707419493</v>
+        <v>0.01293806027683731</v>
       </c>
       <c r="G8">
-        <v>76.16000000000001</v>
+        <v>78.56</v>
       </c>
       <c r="H8">
-        <v>-0.8491643212964515</v>
+        <v>-0.8844602466788515</v>
       </c>
       <c r="I8">
-        <v>4.588932797821692</v>
+        <v>4.598638276372822</v>
       </c>
       <c r="J8">
-        <v>-5.486300570091051E-05</v>
+        <v>-0.0001374879057452028</v>
       </c>
       <c r="K8">
-        <v>0.03051485408746376</v>
+        <v>0.0304816121413715</v>
       </c>
       <c r="L8">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M8">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="N8">
-        <v>0.0008991856708976707</v>
+        <v>0.0007298308337529448</v>
       </c>
       <c r="O8">
-        <v>9.798959221981582E-05</v>
+        <v>6.316190199481711E-05</v>
       </c>
       <c r="P8">
-        <v>-1.066599209025287</v>
+        <v>-1.136689277085605</v>
       </c>
       <c r="Q8">
-        <v>2.526693676457811</v>
+        <v>2.149769781350933</v>
       </c>
       <c r="R8">
-        <v>-0.0003340442893269766</v>
+        <v>-0.00042075036407395</v>
       </c>
       <c r="S8">
-        <v>0.02589477159034883</v>
+        <v>0.02880153759533876</v>
       </c>
       <c r="T8">
-        <v>295</v>
+        <v>236</v>
       </c>
       <c r="U8">
-        <v>475</v>
+        <v>490</v>
       </c>
       <c r="V8">
-        <v>0.00218978612836585</v>
+        <v>0.003243779648000234</v>
       </c>
       <c r="W8">
-        <v>3.785571543126623E-06</v>
+        <v>2.549698974745257E-06</v>
       </c>
     </row>
     <row r="9" spans="1:23">
@@ -990,70 +990,70 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>95.68000000000001</v>
+        <v>91.67999999999999</v>
       </c>
       <c r="C9">
-        <v>0.002617553316373425</v>
+        <v>0.002804609079358821</v>
       </c>
       <c r="D9">
-        <v>135.52</v>
+        <v>136.16</v>
       </c>
       <c r="E9">
-        <v>24.64</v>
+        <v>24.32</v>
       </c>
       <c r="F9">
-        <v>0.0157436605672381</v>
+        <v>0.016144306175159</v>
       </c>
       <c r="G9">
-        <v>66.08</v>
+        <v>65.92</v>
       </c>
       <c r="H9">
-        <v>-0.8370450237240743</v>
+        <v>-0.5014526124883201</v>
       </c>
       <c r="I9">
-        <v>2.902781353520866</v>
+        <v>3.32654300578116</v>
       </c>
       <c r="J9">
-        <v>0.000113887776867466</v>
+        <v>-6.201653490015779E-06</v>
       </c>
       <c r="K9">
-        <v>0.0150377916880895</v>
+        <v>0.01641128642306686</v>
       </c>
       <c r="L9">
-        <v>248</v>
+        <v>277</v>
       </c>
       <c r="M9">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="N9">
-        <v>0.0004756831142825025</v>
+        <v>0.0003555728408532602</v>
       </c>
       <c r="O9">
-        <v>1.660761501716177E-06</v>
+        <v>9.754334591365849E-07</v>
       </c>
       <c r="P9">
-        <v>-0.4697787930459011</v>
+        <v>-0.4168696832751199</v>
       </c>
       <c r="Q9">
-        <v>1.386860669334919</v>
+        <v>1.228492552143189</v>
       </c>
       <c r="R9">
-        <v>0.0002831761142650475</v>
+        <v>-0.0002102113520382637</v>
       </c>
       <c r="S9">
-        <v>0.02996751436151743</v>
+        <v>0.03139895932804017</v>
       </c>
       <c r="T9">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="U9">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="V9">
-        <v>0.0005012384472565072</v>
+        <v>0.0006468615082111331</v>
       </c>
       <c r="W9">
-        <v>2.640774999893631E-05</v>
+        <v>2.320053582268403E-05</v>
       </c>
     </row>
     <row r="10" spans="1:23">
@@ -1061,70 +1061,70 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>21.12</v>
+        <v>21.44</v>
       </c>
       <c r="C10">
-        <v>0.04278861977265875</v>
+        <v>0.0433385039565104</v>
       </c>
       <c r="D10">
         <v>66.55999999999999</v>
       </c>
       <c r="E10">
-        <v>25.28</v>
+        <v>38.08000000000001</v>
       </c>
       <c r="F10">
-        <v>0.02237448185504321</v>
+        <v>0.0217356272540857</v>
       </c>
       <c r="G10">
-        <v>69.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="H10">
-        <v>0.2398255713248025</v>
+        <v>0.2238947946838722</v>
       </c>
       <c r="I10">
-        <v>2.977885709940506</v>
+        <v>3.017811521327035</v>
       </c>
       <c r="J10">
-        <v>-0.0002912686382950547</v>
+        <v>-0.0003462359404600108</v>
       </c>
       <c r="K10">
-        <v>0.05153352390151887</v>
+        <v>0.05257187865497445</v>
       </c>
       <c r="L10">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="M10">
         <v>415</v>
       </c>
       <c r="N10">
-        <v>0.001313834503265043</v>
+        <v>0.001383134866819978</v>
       </c>
       <c r="O10">
-        <v>4.909452615728609E-05</v>
+        <v>4.901229367489552E-05</v>
       </c>
       <c r="P10">
-        <v>0.587817596845857</v>
+        <v>0.482887692008202</v>
       </c>
       <c r="Q10">
-        <v>3.7259679338161</v>
+        <v>3.537202536732666</v>
       </c>
       <c r="R10">
-        <v>-0.0002239271328408037</v>
+        <v>-0.00049919985414336</v>
       </c>
       <c r="S10">
-        <v>0.03210615986299115</v>
+        <v>0.03334878759800297</v>
       </c>
       <c r="T10">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="U10">
-        <v>434</v>
+        <v>504</v>
       </c>
       <c r="V10">
-        <v>0.001024022373068393</v>
+        <v>0.001881086486130078</v>
       </c>
       <c r="W10">
-        <v>7.558357434712283E-06</v>
+        <v>7.643116879641553E-06</v>
       </c>
     </row>
   </sheetData>

--- a/result/xlsx/ecg_analysisresults1.xlsx
+++ b/result/xlsx/ecg_analysisresults1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>rat_number</t>
   </si>
@@ -83,6 +83,84 @@
   </si>
   <si>
     <t>pat_ratio_psd_power</t>
+  </si>
+  <si>
+    <t>norm_phase_instability</t>
+  </si>
+  <si>
+    <t>pat_phase_instability</t>
+  </si>
+  <si>
+    <t>norm_sample_entropy</t>
+  </si>
+  <si>
+    <t>norm_shannon_entropy</t>
+  </si>
+  <si>
+    <t>norm_permutation_entropy</t>
+  </si>
+  <si>
+    <t>pat_sample_entropy</t>
+  </si>
+  <si>
+    <t>pat_shannon_entropy</t>
+  </si>
+  <si>
+    <t>pat_permutation_entropy</t>
+  </si>
+  <si>
+    <t>[1.40550473 0.01773194]</t>
+  </si>
+  <si>
+    <t>[0.53195145 0.10864317]</t>
+  </si>
+  <si>
+    <t>[1.36888522 0.02973707]</t>
+  </si>
+  <si>
+    <t>[1.55445125 0.06600814]</t>
+  </si>
+  <si>
+    <t>[1.28563678 0.03383189]</t>
+  </si>
+  <si>
+    <t>[1.62816064 0.04586117]</t>
+  </si>
+  <si>
+    <t>[1.52036243 0.0359855 ]</t>
+  </si>
+  <si>
+    <t>[1.41241021 0.04436247]</t>
+  </si>
+  <si>
+    <t>[1.23626714 0.02075312]</t>
+  </si>
+  <si>
+    <t>[1.38055312 0.01734788]</t>
+  </si>
+  <si>
+    <t>[1.83269408 0.04991705]</t>
+  </si>
+  <si>
+    <t>[1.1187721  0.02090621]</t>
+  </si>
+  <si>
+    <t>[2.16997755 0.1531576 ]</t>
+  </si>
+  <si>
+    <t>[1.33507234 0.02122987]</t>
+  </si>
+  <si>
+    <t>[1.89959217 0.02579136]</t>
+  </si>
+  <si>
+    <t>[1.49649361 0.02799795]</t>
+  </si>
+  <si>
+    <t>[1.40733499 0.02709869]</t>
+  </si>
+  <si>
+    <t>[1.23424972 0.02353082]</t>
   </si>
 </sst>
 </file>
@@ -414,10 +492,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W10"/>
+  <dimension ref="A1:AE10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:31">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -487,8 +565,32 @@
       <c r="W1" t="s">
         <v>22</v>
       </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:31">
       <c r="A2">
         <v>10</v>
       </c>
@@ -558,8 +660,32 @@
       <c r="W2">
         <v>2.061278578795905E-06</v>
       </c>
+      <c r="X2">
+        <v>0.9932372143591476</v>
+      </c>
+      <c r="Y2">
+        <v>1.818504385977089</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA2">
+        <v>9.965784284662087</v>
+      </c>
+      <c r="AB2">
+        <v>1.270876432001688</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD2">
+        <v>9.965784284662087</v>
+      </c>
+      <c r="AE2">
+        <v>1.199444772579061</v>
+      </c>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:31">
       <c r="A3">
         <v>11</v>
       </c>
@@ -629,8 +755,32 @@
       <c r="W3">
         <v>0.0002132957029321773</v>
       </c>
+      <c r="X3">
+        <v>0.4836223635968391</v>
+      </c>
+      <c r="Y3">
+        <v>0.07286947408172162</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA3">
+        <v>9.965784284662087</v>
+      </c>
+      <c r="AB3">
+        <v>2.446635105035866</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD3">
+        <v>9.965784284662087</v>
+      </c>
+      <c r="AE3">
+        <v>1.203740639847587</v>
+      </c>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:31">
       <c r="A4">
         <v>12</v>
       </c>
@@ -700,8 +850,32 @@
       <c r="W4">
         <v>6.330004307736059E-06</v>
       </c>
+      <c r="X4">
+        <v>0.5100270691198743</v>
+      </c>
+      <c r="Y4">
+        <v>-0.4345191802097597</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA4">
+        <v>9.965784284662087</v>
+      </c>
+      <c r="AB4">
+        <v>1.191386549654506</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD4">
+        <v>9.965784284662087</v>
+      </c>
+      <c r="AE4">
+        <v>1.159559804553066</v>
+      </c>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:31">
       <c r="A5">
         <v>13</v>
       </c>
@@ -771,8 +945,32 @@
       <c r="W5">
         <v>0.01212145719598905</v>
       </c>
+      <c r="X5">
+        <v>-0.2232888102466623</v>
+      </c>
+      <c r="Y5">
+        <v>-0.1912512001229722</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA5">
+        <v>9.965784284662087</v>
+      </c>
+      <c r="AB5">
+        <v>1.296659477128317</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD5">
+        <v>9.965784284662087</v>
+      </c>
+      <c r="AE5">
+        <v>1.813121958423331</v>
+      </c>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:31">
       <c r="A6">
         <v>14</v>
       </c>
@@ -842,8 +1040,32 @@
       <c r="W6">
         <v>8.511598585391653E-05</v>
       </c>
+      <c r="X6">
+        <v>-1.343463302451571</v>
+      </c>
+      <c r="Y6">
+        <v>-1.184909562741106</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA6">
+        <v>9.965784284662087</v>
+      </c>
+      <c r="AB6">
+        <v>1.109950413191423</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD6">
+        <v>9.965784284662087</v>
+      </c>
+      <c r="AE6">
+        <v>1.249820351967356</v>
+      </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:31">
       <c r="A7">
         <v>15</v>
       </c>
@@ -913,8 +1135,32 @@
       <c r="W7">
         <v>4.439594164369012E-06</v>
       </c>
+      <c r="X7">
+        <v>-1.269698071624981</v>
+      </c>
+      <c r="Y7">
+        <v>-0.7200760915669344</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA7">
+        <v>9.965784284662087</v>
+      </c>
+      <c r="AB7">
+        <v>1.057257417772366</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>45</v>
+      </c>
+      <c r="AD7">
+        <v>9.965784284662087</v>
+      </c>
+      <c r="AE7">
+        <v>1.106572840814721</v>
+      </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:31">
       <c r="A8">
         <v>16</v>
       </c>
@@ -984,8 +1230,32 @@
       <c r="W8">
         <v>2.549698974745257E-06</v>
       </c>
+      <c r="X8">
+        <v>-0.1264858932598404</v>
+      </c>
+      <c r="Y8">
+        <v>-0.7263002106974825</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA8">
+        <v>9.965784284662087</v>
+      </c>
+      <c r="AB8">
+        <v>1.174781169098869</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD8">
+        <v>9.965784284662087</v>
+      </c>
+      <c r="AE8">
+        <v>1.136262351128707</v>
+      </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:31">
       <c r="A9">
         <v>17</v>
       </c>
@@ -1055,8 +1325,32 @@
       <c r="W9">
         <v>2.320053582268403E-05</v>
       </c>
+      <c r="X9">
+        <v>-0.1141383132685594</v>
+      </c>
+      <c r="Y9">
+        <v>-0.5966701504409082</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA9">
+        <v>9.965784284662087</v>
+      </c>
+      <c r="AB9">
+        <v>1.160560009297871</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD9">
+        <v>9.965784284662087</v>
+      </c>
+      <c r="AE9">
+        <v>1.303723646754252</v>
+      </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:31">
       <c r="A10">
         <v>18</v>
       </c>
@@ -1125,6 +1419,30 @@
       </c>
       <c r="W10">
         <v>7.643116879641553E-06</v>
+      </c>
+      <c r="X10">
+        <v>-0.6473135889986615</v>
+      </c>
+      <c r="Y10">
+        <v>-1.243262006089833</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA10">
+        <v>9.965784284662087</v>
+      </c>
+      <c r="AB10">
+        <v>1.174853803563651</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD10">
+        <v>9.965784284662087</v>
+      </c>
+      <c r="AE10">
+        <v>1.222330872320572</v>
       </c>
     </row>
   </sheetData>

--- a/result/xlsx/ecg_analysisresults1.xlsx
+++ b/result/xlsx/ecg_analysisresults1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>rat_number</t>
   </si>
@@ -109,58 +109,34 @@
     <t>pat_permutation_entropy</t>
   </si>
   <si>
-    <t>[1.40550473 0.01773194]</t>
-  </si>
-  <si>
-    <t>[0.53195145 0.10864317]</t>
-  </si>
-  <si>
-    <t>[1.36888522 0.02973707]</t>
-  </si>
-  <si>
-    <t>[1.55445125 0.06600814]</t>
-  </si>
-  <si>
-    <t>[1.28563678 0.03383189]</t>
-  </si>
-  <si>
-    <t>[1.62816064 0.04586117]</t>
-  </si>
-  <si>
-    <t>[1.52036243 0.0359855 ]</t>
-  </si>
-  <si>
-    <t>[1.41241021 0.04436247]</t>
-  </si>
-  <si>
-    <t>[1.23626714 0.02075312]</t>
-  </si>
-  <si>
-    <t>[1.38055312 0.01734788]</t>
-  </si>
-  <si>
-    <t>[1.83269408 0.04991705]</t>
-  </si>
-  <si>
-    <t>[1.1187721  0.02090621]</t>
-  </si>
-  <si>
-    <t>[2.16997755 0.1531576 ]</t>
-  </si>
-  <si>
-    <t>[1.33507234 0.02122987]</t>
-  </si>
-  <si>
-    <t>[1.89959217 0.02579136]</t>
-  </si>
-  <si>
-    <t>[1.49649361 0.02799795]</t>
-  </si>
-  <si>
-    <t>[1.40733499 0.02709869]</t>
-  </si>
-  <si>
-    <t>[1.23424972 0.02353082]</t>
+    <t>norm_dfa</t>
+  </si>
+  <si>
+    <t>pat_dfa</t>
+  </si>
+  <si>
+    <t>norm_cwt_freq</t>
+  </si>
+  <si>
+    <t>norm_cwt_time</t>
+  </si>
+  <si>
+    <t>pat_cwt_freq</t>
+  </si>
+  <si>
+    <t>pat_cwt_time</t>
+  </si>
+  <si>
+    <t>norm_max_psd_freq</t>
+  </si>
+  <si>
+    <t>norm_max_psd_psd</t>
+  </si>
+  <si>
+    <t>pat_max_psd_freq</t>
+  </si>
+  <si>
+    <t>pat_max_psd_psd</t>
   </si>
 </sst>
 </file>
@@ -492,10 +468,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE10"/>
+  <dimension ref="A1:AO10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:41">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -589,8 +565,38 @@
       <c r="AE1" t="s">
         <v>30</v>
       </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="2" spans="1:31">
+    <row r="2" spans="1:41">
       <c r="A2">
         <v>10</v>
       </c>
@@ -666,8 +672,8 @@
       <c r="Y2">
         <v>1.818504385977089</v>
       </c>
-      <c r="Z2" t="s">
-        <v>31</v>
+      <c r="Z2">
+        <v>0.7116183354028598</v>
       </c>
       <c r="AA2">
         <v>9.965784284662087</v>
@@ -675,8 +681,8 @@
       <c r="AB2">
         <v>1.270876432001688</v>
       </c>
-      <c r="AC2" t="s">
-        <v>40</v>
+      <c r="AC2">
+        <v>0.6989504989127707</v>
       </c>
       <c r="AD2">
         <v>9.965784284662087</v>
@@ -684,8 +690,38 @@
       <c r="AE2">
         <v>1.199444772579061</v>
       </c>
+      <c r="AF2">
+        <v>2.03566540670961</v>
+      </c>
+      <c r="AG2">
+        <v>2.046158372527649</v>
+      </c>
+      <c r="AH2">
+        <v>390.6249999999999</v>
+      </c>
+      <c r="AI2">
+        <v>0.05541541541541541</v>
+      </c>
+      <c r="AJ2">
+        <v>390.6249999999999</v>
+      </c>
+      <c r="AK2">
+        <v>0.0006406406406406406</v>
+      </c>
+      <c r="AL2">
+        <v>306.25</v>
+      </c>
+      <c r="AM2">
+        <v>2.36606232609558E-09</v>
+      </c>
+      <c r="AN2">
+        <v>362.5</v>
+      </c>
+      <c r="AO2">
+        <v>5.79262361723683E-11</v>
+      </c>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" spans="1:41">
       <c r="A3">
         <v>11</v>
       </c>
@@ -761,8 +797,8 @@
       <c r="Y3">
         <v>0.07286947408172162</v>
       </c>
-      <c r="Z3" t="s">
-        <v>32</v>
+      <c r="Z3">
+        <v>0.3202973096608772</v>
       </c>
       <c r="AA3">
         <v>9.965784284662087</v>
@@ -770,8 +806,8 @@
       <c r="AB3">
         <v>2.446635105035866</v>
       </c>
-      <c r="AC3" t="s">
-        <v>41</v>
+      <c r="AC3">
+        <v>0.9413055672637527</v>
       </c>
       <c r="AD3">
         <v>9.965784284662087</v>
@@ -779,8 +815,38 @@
       <c r="AE3">
         <v>1.203740639847587</v>
       </c>
+      <c r="AF3">
+        <v>0.5314013363148092</v>
+      </c>
+      <c r="AG3">
+        <v>1.846077395115045</v>
+      </c>
+      <c r="AH3">
+        <v>461.6477272727273</v>
+      </c>
+      <c r="AI3">
+        <v>0.09017017017017016</v>
+      </c>
+      <c r="AJ3">
+        <v>390.6249999999999</v>
+      </c>
+      <c r="AK3">
+        <v>0.05765765765765766</v>
+      </c>
+      <c r="AL3">
+        <v>500</v>
+      </c>
+      <c r="AM3">
+        <v>7.643984895220215E-08</v>
+      </c>
+      <c r="AN3">
+        <v>362.5</v>
+      </c>
+      <c r="AO3">
+        <v>4.646883324472991E-09</v>
+      </c>
     </row>
-    <row r="4" spans="1:31">
+    <row r="4" spans="1:41">
       <c r="A4">
         <v>12</v>
       </c>
@@ -856,8 +922,8 @@
       <c r="Y4">
         <v>-0.4345191802097597</v>
       </c>
-      <c r="Z4" t="s">
-        <v>33</v>
+      <c r="Z4">
+        <v>0.6993111454988198</v>
       </c>
       <c r="AA4">
         <v>9.965784284662087</v>
@@ -865,8 +931,8 @@
       <c r="AB4">
         <v>1.191386549654506</v>
       </c>
-      <c r="AC4" t="s">
-        <v>42</v>
+      <c r="AC4">
+        <v>0.5698391534768681</v>
       </c>
       <c r="AD4">
         <v>9.965784284662087</v>
@@ -874,8 +940,38 @@
       <c r="AE4">
         <v>1.159559804553066</v>
       </c>
+      <c r="AF4">
+        <v>1.865147774102489</v>
+      </c>
+      <c r="AG4">
+        <v>1.913513735038579</v>
+      </c>
+      <c r="AH4">
+        <v>390.6249999999999</v>
+      </c>
+      <c r="AI4">
+        <v>0.1595195195195195</v>
+      </c>
+      <c r="AJ4">
+        <v>390.6249999999999</v>
+      </c>
+      <c r="AK4">
+        <v>0.1595195195195195</v>
+      </c>
+      <c r="AL4">
+        <v>306.25</v>
+      </c>
+      <c r="AM4">
+        <v>3.669119746412307E-09</v>
+      </c>
+      <c r="AN4">
+        <v>312.5</v>
+      </c>
+      <c r="AO4">
+        <v>5.900331929375982E-10</v>
+      </c>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" spans="1:41">
       <c r="A5">
         <v>13</v>
       </c>
@@ -951,8 +1047,8 @@
       <c r="Y5">
         <v>-0.1912512001229722</v>
       </c>
-      <c r="Z5" t="s">
-        <v>34</v>
+      <c r="Z5">
+        <v>0.8102296936639212</v>
       </c>
       <c r="AA5">
         <v>9.965784284662087</v>
@@ -960,8 +1056,8 @@
       <c r="AB5">
         <v>1.296659477128317</v>
       </c>
-      <c r="AC5" t="s">
-        <v>43</v>
+      <c r="AC5">
+        <v>1.161567573345453</v>
       </c>
       <c r="AD5">
         <v>9.965784284662087</v>
@@ -969,8 +1065,38 @@
       <c r="AE5">
         <v>1.813121958423331</v>
       </c>
+      <c r="AF5">
+        <v>1.884271785758477</v>
+      </c>
+      <c r="AG5">
+        <v>1.745967209410987</v>
+      </c>
+      <c r="AH5">
+        <v>390.6249999999999</v>
+      </c>
+      <c r="AI5">
+        <v>0.1595195195195195</v>
+      </c>
+      <c r="AJ5">
+        <v>390.6249999999999</v>
+      </c>
+      <c r="AK5">
+        <v>0.0006406406406406406</v>
+      </c>
+      <c r="AL5">
+        <v>375</v>
+      </c>
+      <c r="AM5">
+        <v>2.315546464713939E-10</v>
+      </c>
+      <c r="AN5">
+        <v>300</v>
+      </c>
+      <c r="AO5">
+        <v>1.049862541187762E-08</v>
+      </c>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" spans="1:41">
       <c r="A6">
         <v>14</v>
       </c>
@@ -1046,8 +1172,8 @@
       <c r="Y6">
         <v>-1.184909562741106</v>
       </c>
-      <c r="Z6" t="s">
-        <v>35</v>
+      <c r="Z6">
+        <v>0.6597343338830682</v>
       </c>
       <c r="AA6">
         <v>9.965784284662087</v>
@@ -1055,8 +1181,8 @@
       <c r="AB6">
         <v>1.109950413191423</v>
       </c>
-      <c r="AC6" t="s">
-        <v>44</v>
+      <c r="AC6">
+        <v>0.678151104817902</v>
       </c>
       <c r="AD6">
         <v>9.965784284662087</v>
@@ -1064,8 +1190,38 @@
       <c r="AE6">
         <v>1.249820351967356</v>
       </c>
+      <c r="AF6">
+        <v>1.870263305875198</v>
+      </c>
+      <c r="AG6">
+        <v>1.919659023244198</v>
+      </c>
+      <c r="AH6">
+        <v>390.6249999999999</v>
+      </c>
+      <c r="AI6">
+        <v>0.0006406406406406406</v>
+      </c>
+      <c r="AJ6">
+        <v>390.6249999999999</v>
+      </c>
+      <c r="AK6">
+        <v>0.05925925925925925</v>
+      </c>
+      <c r="AL6">
+        <v>362.5</v>
+      </c>
+      <c r="AM6">
+        <v>2.451650626910585E-10</v>
+      </c>
+      <c r="AN6">
+        <v>300</v>
+      </c>
+      <c r="AO6">
+        <v>1.719581102872684E-09</v>
+      </c>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" spans="1:41">
       <c r="A7">
         <v>15</v>
       </c>
@@ -1141,8 +1297,8 @@
       <c r="Y7">
         <v>-0.7200760915669344</v>
       </c>
-      <c r="Z7" t="s">
-        <v>36</v>
+      <c r="Z7">
+        <v>0.8370109066566809</v>
       </c>
       <c r="AA7">
         <v>9.965784284662087</v>
@@ -1150,8 +1306,8 @@
       <c r="AB7">
         <v>1.057257417772366</v>
       </c>
-      <c r="AC7" t="s">
-        <v>45</v>
+      <c r="AC7">
+        <v>0.9626917651194119</v>
       </c>
       <c r="AD7">
         <v>9.965784284662087</v>
@@ -1159,8 +1315,38 @@
       <c r="AE7">
         <v>1.106572840814721</v>
       </c>
+      <c r="AF7">
+        <v>1.96664353017616</v>
+      </c>
+      <c r="AG7">
+        <v>2.038893231648245</v>
+      </c>
+      <c r="AH7">
+        <v>390.6249999999999</v>
+      </c>
+      <c r="AI7">
+        <v>0.0590990990990991</v>
+      </c>
+      <c r="AJ7">
+        <v>390.6249999999999</v>
+      </c>
+      <c r="AK7">
+        <v>0.1595195195195195</v>
+      </c>
+      <c r="AL7">
+        <v>300</v>
+      </c>
+      <c r="AM7">
+        <v>2.055247385039394E-09</v>
+      </c>
+      <c r="AN7">
+        <v>312.5</v>
+      </c>
+      <c r="AO7">
+        <v>1.639566608964256E-10</v>
+      </c>
     </row>
-    <row r="8" spans="1:31">
+    <row r="8" spans="1:41">
       <c r="A8">
         <v>16</v>
       </c>
@@ -1236,8 +1422,8 @@
       <c r="Y8">
         <v>-0.7263002106974825</v>
       </c>
-      <c r="Z8" t="s">
-        <v>37</v>
+      <c r="Z8">
+        <v>0.7781739673753777</v>
       </c>
       <c r="AA8">
         <v>9.965784284662087</v>
@@ -1245,8 +1431,8 @@
       <c r="AB8">
         <v>1.174781169098869</v>
       </c>
-      <c r="AC8" t="s">
-        <v>46</v>
+      <c r="AC8">
+        <v>0.7622457811876209</v>
       </c>
       <c r="AD8">
         <v>9.965784284662087</v>
@@ -1254,8 +1440,38 @@
       <c r="AE8">
         <v>1.136262351128707</v>
       </c>
+      <c r="AF8">
+        <v>1.777054446509016</v>
+      </c>
+      <c r="AG8">
+        <v>1.957118712207264</v>
+      </c>
+      <c r="AH8">
+        <v>390.6249999999999</v>
+      </c>
+      <c r="AI8">
+        <v>0.05717717717717718</v>
+      </c>
+      <c r="AJ8">
+        <v>390.6249999999999</v>
+      </c>
+      <c r="AK8">
+        <v>0.0006406406406406406</v>
+      </c>
+      <c r="AL8">
+        <v>425</v>
+      </c>
+      <c r="AM8">
+        <v>1.441062988329308E-09</v>
+      </c>
+      <c r="AN8">
+        <v>362.5</v>
+      </c>
+      <c r="AO8">
+        <v>5.467928470434647E-11</v>
+      </c>
     </row>
-    <row r="9" spans="1:31">
+    <row r="9" spans="1:41">
       <c r="A9">
         <v>17</v>
       </c>
@@ -1331,8 +1547,8 @@
       <c r="Y9">
         <v>-0.5966701504409082</v>
       </c>
-      <c r="Z9" t="s">
-        <v>38</v>
+      <c r="Z9">
+        <v>0.7283863384086773</v>
       </c>
       <c r="AA9">
         <v>9.965784284662087</v>
@@ -1340,8 +1556,8 @@
       <c r="AB9">
         <v>1.160560009297871</v>
       </c>
-      <c r="AC9" t="s">
-        <v>47</v>
+      <c r="AC9">
+        <v>0.7172168430400329</v>
       </c>
       <c r="AD9">
         <v>9.965784284662087</v>
@@ -1349,8 +1565,38 @@
       <c r="AE9">
         <v>1.303723646754252</v>
       </c>
+      <c r="AF9">
+        <v>1.854921656632994</v>
+      </c>
+      <c r="AG9">
+        <v>1.902692101579325</v>
+      </c>
+      <c r="AH9">
+        <v>390.6249999999999</v>
+      </c>
+      <c r="AI9">
+        <v>0.1595195195195195</v>
+      </c>
+      <c r="AJ9">
+        <v>390.6249999999999</v>
+      </c>
+      <c r="AK9">
+        <v>0.04868868868868869</v>
+      </c>
+      <c r="AL9">
+        <v>468.75</v>
+      </c>
+      <c r="AM9">
+        <v>1.030616001222443E-11</v>
+      </c>
+      <c r="AN9">
+        <v>362.5</v>
+      </c>
+      <c r="AO9">
+        <v>6.835341046508541E-10</v>
+      </c>
     </row>
-    <row r="10" spans="1:31">
+    <row r="10" spans="1:41">
       <c r="A10">
         <v>18</v>
       </c>
@@ -1426,8 +1672,8 @@
       <c r="Y10">
         <v>-1.243262006089833</v>
       </c>
-      <c r="Z10" t="s">
-        <v>39</v>
+      <c r="Z10">
+        <v>0.6285101330944131</v>
       </c>
       <c r="AA10">
         <v>9.965784284662087</v>
@@ -1435,14 +1681,44 @@
       <c r="AB10">
         <v>1.174853803563651</v>
       </c>
-      <c r="AC10" t="s">
-        <v>48</v>
+      <c r="AC10">
+        <v>0.6288902702436737</v>
       </c>
       <c r="AD10">
         <v>9.965784284662087</v>
       </c>
       <c r="AE10">
         <v>1.222330872320572</v>
+      </c>
+      <c r="AF10">
+        <v>1.917754904105347</v>
+      </c>
+      <c r="AG10">
+        <v>2.004823462164662</v>
+      </c>
+      <c r="AH10">
+        <v>390.6249999999999</v>
+      </c>
+      <c r="AI10">
+        <v>0.0006406406406406406</v>
+      </c>
+      <c r="AJ10">
+        <v>390.6249999999999</v>
+      </c>
+      <c r="AK10">
+        <v>0.0006406406406406406</v>
+      </c>
+      <c r="AL10">
+        <v>300</v>
+      </c>
+      <c r="AM10">
+        <v>5.30827197662145E-09</v>
+      </c>
+      <c r="AN10">
+        <v>337.5</v>
+      </c>
+      <c r="AO10">
+        <v>2.18751583240337E-10</v>
       </c>
     </row>
   </sheetData>

--- a/result/xlsx/ecg_analysisresults1.xlsx
+++ b/result/xlsx/ecg_analysisresults1.xlsx
@@ -619,16 +619,16 @@
         <v>71.36000000000001</v>
       </c>
       <c r="H2">
-        <v>-2.91799720136641</v>
+        <v>-0.9366863432781714</v>
       </c>
       <c r="I2">
-        <v>9.487728105939796</v>
+        <v>6.644959115359029</v>
       </c>
       <c r="J2">
-        <v>-0.000565788861687424</v>
+        <v>0.0001255827722156283</v>
       </c>
       <c r="K2">
-        <v>0.04637570178724547</v>
+        <v>0.02011357995977272</v>
       </c>
       <c r="L2">
         <v>283</v>
@@ -643,16 +643,16 @@
         <v>8.439569881246977E-05</v>
       </c>
       <c r="P2">
-        <v>-1.097062782219975</v>
+        <v>-1.117211836098308</v>
       </c>
       <c r="Q2">
-        <v>2.537530552679585</v>
+        <v>7.344357950826364</v>
       </c>
       <c r="R2">
-        <v>-0.001828023599046852</v>
+        <v>-0.0001286210632024672</v>
       </c>
       <c r="S2">
-        <v>0.02851497604107792</v>
+        <v>0.006806018916718589</v>
       </c>
       <c r="T2">
         <v>278</v>
@@ -673,22 +673,22 @@
         <v>1.818504385977089</v>
       </c>
       <c r="Z2">
-        <v>0.7116183354028598</v>
+        <v>0.4175768410582319</v>
       </c>
       <c r="AA2">
         <v>9.965784284662087</v>
       </c>
       <c r="AB2">
-        <v>1.270876432001688</v>
+        <v>1.246203955693171</v>
       </c>
       <c r="AC2">
-        <v>0.6989504989127707</v>
+        <v>0.6339332219551713</v>
       </c>
       <c r="AD2">
         <v>9.965784284662087</v>
       </c>
       <c r="AE2">
-        <v>1.199444772579061</v>
+        <v>1.195365682041001</v>
       </c>
       <c r="AF2">
         <v>2.03566540670961</v>
@@ -744,16 +744,16 @@
         <v>64.8</v>
       </c>
       <c r="H3">
-        <v>-0.005034429458719266</v>
+        <v>0.8043445185423629</v>
       </c>
       <c r="I3">
-        <v>8.819301343365815</v>
+        <v>2.350531977197557</v>
       </c>
       <c r="J3">
-        <v>1.308879340764767E-05</v>
+        <v>-2.620781649665656E-05</v>
       </c>
       <c r="K3">
-        <v>0.002886567095355565</v>
+        <v>0.0005437695769222536</v>
       </c>
       <c r="L3">
         <v>438</v>
@@ -768,16 +768,16 @@
         <v>0.8575770384199922</v>
       </c>
       <c r="P3">
-        <v>-1.064347071408852</v>
+        <v>-0.7096635459538118</v>
       </c>
       <c r="Q3">
-        <v>0.1642435992607978</v>
+        <v>4.952620393127704</v>
       </c>
       <c r="R3">
-        <v>0.0008846246880419261</v>
+        <v>5.346411873472015E-05</v>
       </c>
       <c r="S3">
-        <v>0.0306158876993277</v>
+        <v>0.009290643887838098</v>
       </c>
       <c r="T3">
         <v>193</v>
@@ -798,22 +798,22 @@
         <v>0.07286947408172162</v>
       </c>
       <c r="Z3">
-        <v>0.3202973096608772</v>
+        <v>0.9796574540247226</v>
       </c>
       <c r="AA3">
         <v>9.965784284662087</v>
       </c>
       <c r="AB3">
-        <v>2.446635105035866</v>
+        <v>1.421132495269458</v>
       </c>
       <c r="AC3">
-        <v>0.9413055672637527</v>
+        <v>0.8573102440953293</v>
       </c>
       <c r="AD3">
         <v>9.965784284662087</v>
       </c>
       <c r="AE3">
-        <v>1.203740639847587</v>
+        <v>1.210442180091677</v>
       </c>
       <c r="AF3">
         <v>0.5314013363148092</v>
@@ -869,16 +869,16 @@
         <v>83.68000000000001</v>
       </c>
       <c r="H4">
-        <v>-2.749823940923068</v>
+        <v>-0.2003571700572042</v>
       </c>
       <c r="I4">
-        <v>7.989515616789749</v>
+        <v>9.844786410025568</v>
       </c>
       <c r="J4">
-        <v>0.0008878245845468591</v>
+        <v>-5.141011092989093E-05</v>
       </c>
       <c r="K4">
-        <v>0.04102558351112833</v>
+        <v>0.01851481106079185</v>
       </c>
       <c r="L4">
         <v>259</v>
@@ -893,16 +893,16 @@
         <v>6.636005579377209E-05</v>
       </c>
       <c r="P4">
-        <v>-0.6067122499398648</v>
+        <v>0.8579322715742234</v>
       </c>
       <c r="Q4">
-        <v>2.812309923944136</v>
+        <v>6.857850732758875</v>
       </c>
       <c r="R4">
-        <v>-7.812630022722455E-05</v>
+        <v>2.727161734355893E-05</v>
       </c>
       <c r="S4">
-        <v>0.0529306722201914</v>
+        <v>0.01514727414280907</v>
       </c>
       <c r="T4">
         <v>60</v>
@@ -923,22 +923,22 @@
         <v>-0.4345191802097597</v>
       </c>
       <c r="Z4">
-        <v>0.6993111454988198</v>
+        <v>0.3947232189644241</v>
       </c>
       <c r="AA4">
         <v>9.965784284662087</v>
       </c>
       <c r="AB4">
-        <v>1.191386549654506</v>
+        <v>1.202027697767326</v>
       </c>
       <c r="AC4">
-        <v>0.5698391534768681</v>
+        <v>0.5718393818752476</v>
       </c>
       <c r="AD4">
         <v>9.965784284662087</v>
       </c>
       <c r="AE4">
-        <v>1.159559804553066</v>
+        <v>1.157432529486824</v>
       </c>
       <c r="AF4">
         <v>1.865147774102489</v>
@@ -994,16 +994,16 @@
         <v>60.48</v>
       </c>
       <c r="H5">
-        <v>-2.516457918257631</v>
+        <v>-0.7448651885988774</v>
       </c>
       <c r="I5">
-        <v>8.348747943815287</v>
+        <v>8.192290015012906</v>
       </c>
       <c r="J5">
-        <v>-0.0004989709587610644</v>
+        <v>1.339154535721834E-05</v>
       </c>
       <c r="K5">
-        <v>0.01072514995941691</v>
+        <v>0.006361159345423069</v>
       </c>
       <c r="L5">
         <v>75</v>
@@ -1018,16 +1018,16 @@
         <v>0.0001166074689409999</v>
       </c>
       <c r="P5">
-        <v>-0.4848049280043791</v>
+        <v>-0.2679798682074272</v>
       </c>
       <c r="Q5">
-        <v>-0.1210025901395269</v>
+        <v>0.02990514705567282</v>
       </c>
       <c r="R5">
-        <v>-0.003246669872144651</v>
+        <v>3.324046399379691E-05</v>
       </c>
       <c r="S5">
-        <v>0.00979892514100046</v>
+        <v>0.003390367151012191</v>
       </c>
       <c r="T5">
         <v>40</v>
@@ -1048,22 +1048,22 @@
         <v>-0.1912512001229722</v>
       </c>
       <c r="Z5">
-        <v>0.8102296936639212</v>
+        <v>0.7205301513461925</v>
       </c>
       <c r="AA5">
         <v>9.965784284662087</v>
       </c>
       <c r="AB5">
-        <v>1.296659477128317</v>
+        <v>1.218363464633391</v>
       </c>
       <c r="AC5">
-        <v>1.161567573345453</v>
+        <v>1.228020993093113</v>
       </c>
       <c r="AD5">
         <v>9.965784284662087</v>
       </c>
       <c r="AE5">
-        <v>1.813121958423331</v>
+        <v>1.331127024462426</v>
       </c>
       <c r="AF5">
         <v>1.884271785758477</v>
@@ -1119,16 +1119,16 @@
         <v>82.55999999999999</v>
       </c>
       <c r="H6">
-        <v>0.2101468050660911</v>
+        <v>0.4525371913262313</v>
       </c>
       <c r="I6">
-        <v>7.187757737805665</v>
+        <v>8.968166152835961</v>
       </c>
       <c r="J6">
-        <v>-0.0001473155206192475</v>
+        <v>0.0001133087036957358</v>
       </c>
       <c r="K6">
-        <v>0.02068638057084663</v>
+        <v>0.01413329518614045</v>
       </c>
       <c r="L6">
         <v>285</v>
@@ -1143,16 +1143,16 @@
         <v>2.575906305306628E-05</v>
       </c>
       <c r="P6">
-        <v>1.646837224725429</v>
+        <v>0.2981250566118631</v>
       </c>
       <c r="Q6">
-        <v>5.96785241765285</v>
+        <v>8.268258179884965</v>
       </c>
       <c r="R6">
-        <v>-0.003146103464003431</v>
+        <v>9.547595662856386E-06</v>
       </c>
       <c r="S6">
-        <v>0.0257236863352771</v>
+        <v>0.01347385611718908</v>
       </c>
       <c r="T6">
         <v>278</v>
@@ -1173,22 +1173,22 @@
         <v>-1.184909562741106</v>
       </c>
       <c r="Z6">
-        <v>0.6597343338830682</v>
+        <v>0.5585532915080137</v>
       </c>
       <c r="AA6">
         <v>9.965784284662087</v>
       </c>
       <c r="AB6">
-        <v>1.109950413191423</v>
+        <v>1.165901291511937</v>
       </c>
       <c r="AC6">
-        <v>0.678151104817902</v>
+        <v>0.357650338546605</v>
       </c>
       <c r="AD6">
         <v>9.965784284662087</v>
       </c>
       <c r="AE6">
-        <v>1.249820351967356</v>
+        <v>1.160401512891571</v>
       </c>
       <c r="AF6">
         <v>1.870263305875198</v>
@@ -1244,16 +1244,16 @@
         <v>70.56</v>
       </c>
       <c r="H7">
-        <v>1.328375859320212</v>
+        <v>0.7346740030791319</v>
       </c>
       <c r="I7">
-        <v>5.37088628167027</v>
+        <v>6.855780169513805</v>
       </c>
       <c r="J7">
-        <v>0.0009273769980443077</v>
+        <v>3.245736620707301E-05</v>
       </c>
       <c r="K7">
-        <v>0.02839640640096549</v>
+        <v>0.01564437683076316</v>
       </c>
       <c r="L7">
         <v>293</v>
@@ -1268,16 +1268,16 @@
         <v>9.052913858930483E-05</v>
       </c>
       <c r="P7">
-        <v>1.523179775703952</v>
+        <v>1.500278613808188</v>
       </c>
       <c r="Q7">
-        <v>3.0360354400704</v>
+        <v>7.829507740666047</v>
       </c>
       <c r="R7">
-        <v>2.671344715279744E-06</v>
+        <v>2.802054242041337E-05</v>
       </c>
       <c r="S7">
-        <v>0.02708157738562428</v>
+        <v>0.00677764570747657</v>
       </c>
       <c r="T7">
         <v>313</v>
@@ -1298,22 +1298,22 @@
         <v>-0.7200760915669344</v>
       </c>
       <c r="Z7">
-        <v>0.8370109066566809</v>
+        <v>0.7270176676523481</v>
       </c>
       <c r="AA7">
         <v>9.965784284662087</v>
       </c>
       <c r="AB7">
-        <v>1.057257417772366</v>
+        <v>1.153114088600127</v>
       </c>
       <c r="AC7">
-        <v>0.9626917651194119</v>
+        <v>0.5672737969392552</v>
       </c>
       <c r="AD7">
         <v>9.965784284662087</v>
       </c>
       <c r="AE7">
-        <v>1.106572840814721</v>
+        <v>1.170549618803507</v>
       </c>
       <c r="AF7">
         <v>1.96664353017616</v>
@@ -1369,16 +1369,16 @@
         <v>78.56</v>
       </c>
       <c r="H8">
-        <v>-0.8844602466788515</v>
+        <v>0.4006667190376338</v>
       </c>
       <c r="I8">
-        <v>4.598638276372822</v>
+        <v>7.505273343150629</v>
       </c>
       <c r="J8">
-        <v>-0.0001374879057452028</v>
+        <v>9.793340573712928E-05</v>
       </c>
       <c r="K8">
-        <v>0.0304816121413715</v>
+        <v>0.01731319249915041</v>
       </c>
       <c r="L8">
         <v>276</v>
@@ -1393,16 +1393,16 @@
         <v>6.316190199481711E-05</v>
       </c>
       <c r="P8">
-        <v>-1.136689277085605</v>
+        <v>0.1229945835965955</v>
       </c>
       <c r="Q8">
-        <v>2.149769781350933</v>
+        <v>7.898793633567539</v>
       </c>
       <c r="R8">
-        <v>-0.00042075036407395</v>
+        <v>7.250255184383614E-05</v>
       </c>
       <c r="S8">
-        <v>0.02880153759533876</v>
+        <v>0.006589039886347571</v>
       </c>
       <c r="T8">
         <v>236</v>
@@ -1423,22 +1423,22 @@
         <v>-0.7263002106974825</v>
       </c>
       <c r="Z8">
-        <v>0.7781739673753777</v>
+        <v>0.4626879607771888</v>
       </c>
       <c r="AA8">
         <v>9.965784284662087</v>
       </c>
       <c r="AB8">
-        <v>1.174781169098869</v>
+        <v>1.221715118999123</v>
       </c>
       <c r="AC8">
-        <v>0.7622457811876209</v>
+        <v>0.5205939887913505</v>
       </c>
       <c r="AD8">
         <v>9.965784284662087</v>
       </c>
       <c r="AE8">
-        <v>1.136262351128707</v>
+        <v>1.170408091742932</v>
       </c>
       <c r="AF8">
         <v>1.777054446509016</v>
@@ -1494,16 +1494,16 @@
         <v>65.92</v>
       </c>
       <c r="H9">
-        <v>-0.5014526124883201</v>
+        <v>1.583548019554629</v>
       </c>
       <c r="I9">
-        <v>3.32654300578116</v>
+        <v>11.42684882669506</v>
       </c>
       <c r="J9">
-        <v>-6.201653490015779E-06</v>
+        <v>1.92005026196985E-05</v>
       </c>
       <c r="K9">
-        <v>0.01641128642306686</v>
+        <v>0.008658554904037278</v>
       </c>
       <c r="L9">
         <v>277</v>
@@ -1518,16 +1518,16 @@
         <v>9.754334591365849E-07</v>
       </c>
       <c r="P9">
-        <v>-0.4168696832751199</v>
+        <v>-0.05402338115838327</v>
       </c>
       <c r="Q9">
-        <v>1.228492552143189</v>
+        <v>4.311377089090295</v>
       </c>
       <c r="R9">
-        <v>-0.0002102113520382637</v>
+        <v>-0.0001051465168284826</v>
       </c>
       <c r="S9">
-        <v>0.03139895932804017</v>
+        <v>0.008454296271040681</v>
       </c>
       <c r="T9">
         <v>259</v>
@@ -1548,22 +1548,22 @@
         <v>-0.5966701504409082</v>
       </c>
       <c r="Z9">
-        <v>0.7283863384086773</v>
+        <v>0.714773367023011</v>
       </c>
       <c r="AA9">
         <v>9.965784284662087</v>
       </c>
       <c r="AB9">
-        <v>1.160560009297871</v>
+        <v>1.150344867297527</v>
       </c>
       <c r="AC9">
-        <v>0.7172168430400329</v>
+        <v>0.5794872787573536</v>
       </c>
       <c r="AD9">
         <v>9.965784284662087</v>
       </c>
       <c r="AE9">
-        <v>1.303723646754252</v>
+        <v>1.235657833786838</v>
       </c>
       <c r="AF9">
         <v>1.854921656632994</v>
@@ -1619,16 +1619,16 @@
         <v>80.8</v>
       </c>
       <c r="H10">
-        <v>0.2238947946838722</v>
+        <v>0.998335252576357</v>
       </c>
       <c r="I10">
-        <v>3.017811521327035</v>
+        <v>7.976318079681183</v>
       </c>
       <c r="J10">
-        <v>-0.0003462359404600108</v>
+        <v>0.0002933110893888252</v>
       </c>
       <c r="K10">
-        <v>0.05257187865497445</v>
+        <v>0.02245515896413578</v>
       </c>
       <c r="L10">
         <v>281</v>
@@ -1643,16 +1643,16 @@
         <v>4.901229367489552E-05</v>
       </c>
       <c r="P10">
-        <v>0.482887692008202</v>
+        <v>0.9398027709548687</v>
       </c>
       <c r="Q10">
-        <v>3.537202536732666</v>
+        <v>6.496598040642594</v>
       </c>
       <c r="R10">
-        <v>-0.00049919985414336</v>
+        <v>0.0001336153169968175</v>
       </c>
       <c r="S10">
-        <v>0.03334878759800297</v>
+        <v>0.011158815480567</v>
       </c>
       <c r="T10">
         <v>266</v>
@@ -1673,22 +1673,22 @@
         <v>-1.243262006089833</v>
       </c>
       <c r="Z10">
-        <v>0.6285101330944131</v>
+        <v>0.5626785779216068</v>
       </c>
       <c r="AA10">
         <v>9.965784284662087</v>
       </c>
       <c r="AB10">
-        <v>1.174853803563651</v>
+        <v>1.143287997758899</v>
       </c>
       <c r="AC10">
-        <v>0.6288902702436737</v>
+        <v>0.6307564245031441</v>
       </c>
       <c r="AD10">
         <v>9.965784284662087</v>
       </c>
       <c r="AE10">
-        <v>1.222330872320572</v>
+        <v>1.17274572817694</v>
       </c>
       <c r="AF10">
         <v>1.917754904105347</v>

--- a/result/xlsx/ecg_analysisresults1.xlsx
+++ b/result/xlsx/ecg_analysisresults1.xlsx
@@ -604,31 +604,31 @@
         <v>34.24</v>
       </c>
       <c r="C2">
-        <v>0.03989002784726506</v>
+        <v>0.03988718121379908</v>
       </c>
       <c r="D2">
         <v>79.68000000000001</v>
       </c>
       <c r="E2">
-        <v>26.72</v>
+        <v>25.28</v>
       </c>
       <c r="F2">
-        <v>0.01320625744209405</v>
+        <v>0.01292552526827378</v>
       </c>
       <c r="G2">
-        <v>71.36000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="H2">
-        <v>-0.9366863432781714</v>
+        <v>-0.9366859855049791</v>
       </c>
       <c r="I2">
-        <v>6.644959115359029</v>
+        <v>6.644801118072245</v>
       </c>
       <c r="J2">
-        <v>0.0001255827722156283</v>
+        <v>0.0001257185227048682</v>
       </c>
       <c r="K2">
-        <v>0.02011357995977272</v>
+        <v>0.02011222114640394</v>
       </c>
       <c r="L2">
         <v>283</v>
@@ -637,64 +637,64 @@
         <v>497</v>
       </c>
       <c r="N2">
-        <v>0.001388430588468457</v>
+        <v>0.001381390648510417</v>
       </c>
       <c r="O2">
-        <v>8.439569881246977E-05</v>
+        <v>8.352331622711205E-05</v>
       </c>
       <c r="P2">
-        <v>-1.117211836098308</v>
+        <v>-1.079137812436829</v>
       </c>
       <c r="Q2">
-        <v>7.344357950826364</v>
+        <v>7.096766402942645</v>
       </c>
       <c r="R2">
-        <v>-0.0001286210632024672</v>
+        <v>-0.0001492720407131346</v>
       </c>
       <c r="S2">
-        <v>0.006806018916718589</v>
+        <v>0.006751922355991621</v>
       </c>
       <c r="T2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="U2">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="V2">
-        <v>0.001911950034725556</v>
+        <v>0.002200941015388551</v>
       </c>
       <c r="W2">
-        <v>2.061278578795905E-06</v>
+        <v>2.162577157415963E-06</v>
       </c>
       <c r="X2">
-        <v>0.9932372143591476</v>
+        <v>0.9930414869625246</v>
       </c>
       <c r="Y2">
-        <v>1.818504385977089</v>
+        <v>1.815699441796688</v>
       </c>
       <c r="Z2">
-        <v>0.4175768410582319</v>
+        <v>0.4175791485393163</v>
       </c>
       <c r="AA2">
         <v>9.965784284662087</v>
       </c>
       <c r="AB2">
-        <v>1.246203955693171</v>
+        <v>1.244382346231208</v>
       </c>
       <c r="AC2">
-        <v>0.6339332219551713</v>
+        <v>0.6584327076121851</v>
       </c>
       <c r="AD2">
         <v>9.965784284662087</v>
       </c>
       <c r="AE2">
-        <v>1.195365682041001</v>
+        <v>1.198371848633087</v>
       </c>
       <c r="AF2">
-        <v>2.03566540670961</v>
+        <v>2.035708374450758</v>
       </c>
       <c r="AG2">
-        <v>2.046158372527649</v>
+        <v>2.043139561618361</v>
       </c>
       <c r="AH2">
         <v>390.6249999999999</v>
@@ -712,13 +712,13 @@
         <v>306.25</v>
       </c>
       <c r="AM2">
-        <v>2.36606232609558E-09</v>
+        <v>2.340759465174268E-09</v>
       </c>
       <c r="AN2">
         <v>362.5</v>
       </c>
       <c r="AO2">
-        <v>5.79262361723683E-11</v>
+        <v>7.535181914093295E-11</v>
       </c>
     </row>
     <row r="3" spans="1:41">
@@ -726,58 +726,58 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>80</v>
+        <v>100.32</v>
       </c>
       <c r="C3">
-        <v>0.0005009595324494126</v>
+        <v>0.0005217011930663157</v>
       </c>
       <c r="D3">
-        <v>150.24</v>
+        <v>130.24</v>
       </c>
       <c r="E3">
         <v>33.76</v>
       </c>
       <c r="F3">
-        <v>0.01732683839407854</v>
+        <v>0.01735600618586836</v>
       </c>
       <c r="G3">
         <v>64.8</v>
       </c>
       <c r="H3">
-        <v>0.8043445185423629</v>
+        <v>1.242968239107511</v>
       </c>
       <c r="I3">
-        <v>2.350531977197557</v>
+        <v>3.017418086520411</v>
       </c>
       <c r="J3">
-        <v>-2.620781649665656E-05</v>
+        <v>1.340196285910187E-05</v>
       </c>
       <c r="K3">
-        <v>0.0005437695769222536</v>
+        <v>0.0005566519824257664</v>
       </c>
       <c r="L3">
-        <v>438</v>
+        <v>186</v>
       </c>
       <c r="M3">
-        <v>938</v>
+        <v>813</v>
       </c>
       <c r="N3">
-        <v>0.7782237877830444</v>
+        <v>0.7751438881385536</v>
       </c>
       <c r="O3">
-        <v>0.8575770384199922</v>
+        <v>0.8674669345564118</v>
       </c>
       <c r="P3">
-        <v>-0.7096635459538118</v>
+        <v>-0.7095482207435488</v>
       </c>
       <c r="Q3">
-        <v>4.952620393127704</v>
+        <v>5.00438551428484</v>
       </c>
       <c r="R3">
-        <v>5.346411873472015E-05</v>
+        <v>5.380526374912128E-05</v>
       </c>
       <c r="S3">
-        <v>0.009290643887838098</v>
+        <v>0.009305605763548237</v>
       </c>
       <c r="T3">
         <v>193</v>
@@ -786,40 +786,40 @@
         <v>404</v>
       </c>
       <c r="V3">
-        <v>0.003166355859813709</v>
+        <v>0.003148591052832102</v>
       </c>
       <c r="W3">
-        <v>0.0002132957029321773</v>
+        <v>0.000211368715575516</v>
       </c>
       <c r="X3">
-        <v>0.4836223635968391</v>
+        <v>0.1867669772311749</v>
       </c>
       <c r="Y3">
-        <v>0.07286947408172162</v>
+        <v>0.0742779001585635</v>
       </c>
       <c r="Z3">
-        <v>0.9796574540247226</v>
+        <v>0.9668206874279652</v>
       </c>
       <c r="AA3">
         <v>9.965784284662087</v>
       </c>
       <c r="AB3">
-        <v>1.421132495269458</v>
+        <v>1.401257400076428</v>
       </c>
       <c r="AC3">
-        <v>0.8573102440953293</v>
+        <v>0.8563825639731967</v>
       </c>
       <c r="AD3">
         <v>9.965784284662087</v>
       </c>
       <c r="AE3">
-        <v>1.210442180091677</v>
+        <v>1.211947891363247</v>
       </c>
       <c r="AF3">
-        <v>0.5314013363148092</v>
+        <v>0.5468350877456614</v>
       </c>
       <c r="AG3">
-        <v>1.846077395115045</v>
+        <v>1.845723043298969</v>
       </c>
       <c r="AH3">
         <v>461.6477272727273</v>
@@ -837,13 +837,13 @@
         <v>500</v>
       </c>
       <c r="AM3">
-        <v>7.643984895220215E-08</v>
+        <v>7.290798791304621E-08</v>
       </c>
       <c r="AN3">
         <v>362.5</v>
       </c>
       <c r="AO3">
-        <v>4.646883324472991E-09</v>
+        <v>4.689644537234389E-09</v>
       </c>
     </row>
     <row r="4" spans="1:41">
@@ -854,31 +854,31 @@
         <v>29.76</v>
       </c>
       <c r="C4">
-        <v>0.03663689475000673</v>
+        <v>0.03663696190522749</v>
       </c>
       <c r="D4">
         <v>71.36000000000001</v>
       </c>
       <c r="E4">
-        <v>73.92</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="F4">
-        <v>0.02935096252591826</v>
+        <v>0.02902961265608281</v>
       </c>
       <c r="G4">
         <v>83.68000000000001</v>
       </c>
       <c r="H4">
-        <v>-0.2003571700572042</v>
+        <v>-0.1998715112090076</v>
       </c>
       <c r="I4">
-        <v>9.844786410025568</v>
+        <v>9.843793977214043</v>
       </c>
       <c r="J4">
-        <v>-5.141011092989093E-05</v>
+        <v>-5.136011389084824E-05</v>
       </c>
       <c r="K4">
-        <v>0.01851481106079185</v>
+        <v>0.01851484683848416</v>
       </c>
       <c r="L4">
         <v>259</v>
@@ -887,64 +887,64 @@
         <v>445</v>
       </c>
       <c r="N4">
-        <v>0.001144086673244057</v>
+        <v>0.001145382160993332</v>
       </c>
       <c r="O4">
-        <v>6.636005579377209E-05</v>
+        <v>6.679230166322715E-05</v>
       </c>
       <c r="P4">
-        <v>0.8579322715742234</v>
+        <v>0.8795890077218631</v>
       </c>
       <c r="Q4">
-        <v>6.857850732758875</v>
+        <v>6.726899775548087</v>
       </c>
       <c r="R4">
-        <v>2.727161734355893E-05</v>
+        <v>2.540957763764956E-05</v>
       </c>
       <c r="S4">
-        <v>0.01514727414280907</v>
+        <v>0.01500561335548353</v>
       </c>
       <c r="T4">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="U4">
         <v>522</v>
       </c>
       <c r="V4">
-        <v>0.000153868265623586</v>
+        <v>0.0001440742968675188</v>
       </c>
       <c r="W4">
-        <v>6.330004307736059E-06</v>
+        <v>6.792161775086165E-06</v>
       </c>
       <c r="X4">
-        <v>0.5100270691198743</v>
+        <v>0.5103658219644527</v>
       </c>
       <c r="Y4">
-        <v>-0.4345191802097597</v>
+        <v>-0.4465630706412211</v>
       </c>
       <c r="Z4">
-        <v>0.3947232189644241</v>
+        <v>0.3946769290972429</v>
       </c>
       <c r="AA4">
         <v>9.965784284662087</v>
       </c>
       <c r="AB4">
-        <v>1.202027697767326</v>
+        <v>1.202937276107181</v>
       </c>
       <c r="AC4">
-        <v>0.5718393818752476</v>
+        <v>0.5949984252349811</v>
       </c>
       <c r="AD4">
         <v>9.965784284662087</v>
       </c>
       <c r="AE4">
-        <v>1.157432529486824</v>
+        <v>1.144462570328436</v>
       </c>
       <c r="AF4">
-        <v>1.865147774102489</v>
+        <v>1.865114888740882</v>
       </c>
       <c r="AG4">
-        <v>1.913513735038579</v>
+        <v>1.915322159691681</v>
       </c>
       <c r="AH4">
         <v>390.6249999999999</v>
@@ -962,13 +962,13 @@
         <v>306.25</v>
       </c>
       <c r="AM4">
-        <v>3.669119746412307E-09</v>
+        <v>3.679552740509191E-09</v>
       </c>
       <c r="AN4">
-        <v>312.5</v>
+        <v>306.25</v>
       </c>
       <c r="AO4">
-        <v>5.900331929375982E-10</v>
+        <v>5.540800703841373E-10</v>
       </c>
     </row>
     <row r="5" spans="1:41">
@@ -976,100 +976,100 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>129.28</v>
+        <v>129.92</v>
       </c>
       <c r="C5">
-        <v>0.002805363799071066</v>
+        <v>0.002756607733624587</v>
       </c>
       <c r="D5">
-        <v>141.44</v>
+        <v>142.4</v>
       </c>
       <c r="E5">
-        <v>53.92</v>
+        <v>54.72</v>
       </c>
       <c r="F5">
-        <v>0.003760057799617352</v>
+        <v>0.004648959205415257</v>
       </c>
       <c r="G5">
-        <v>60.48</v>
+        <v>60.96</v>
       </c>
       <c r="H5">
-        <v>-0.7448651885988774</v>
+        <v>-0.7155932294747418</v>
       </c>
       <c r="I5">
-        <v>8.192290015012906</v>
+        <v>7.947747306009594</v>
       </c>
       <c r="J5">
-        <v>1.339154535721834E-05</v>
+        <v>1.68593957300579E-05</v>
       </c>
       <c r="K5">
-        <v>0.006361159345423069</v>
+        <v>0.006622694403049231</v>
       </c>
       <c r="L5">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M5">
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="N5">
-        <v>0.001692661056668869</v>
+        <v>0.001474180680369127</v>
       </c>
       <c r="O5">
-        <v>0.0001166074689409999</v>
+        <v>0.0001011714166639064</v>
       </c>
       <c r="P5">
-        <v>-0.2679798682074272</v>
+        <v>-0.5622186856131701</v>
       </c>
       <c r="Q5">
-        <v>0.02990514705567282</v>
+        <v>0.7516049062442418</v>
       </c>
       <c r="R5">
-        <v>3.324046399379691E-05</v>
+        <v>5.492636872363443E-05</v>
       </c>
       <c r="S5">
-        <v>0.003390367151012191</v>
+        <v>0.003419219182383382</v>
       </c>
       <c r="T5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="U5">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="V5">
-        <v>0.04492601689670915</v>
+        <v>0.04670125981591859</v>
       </c>
       <c r="W5">
-        <v>0.01212145719598905</v>
+        <v>0.01165338320684649</v>
       </c>
       <c r="X5">
-        <v>-0.2232888102466623</v>
+        <v>-0.3542543036671609</v>
       </c>
       <c r="Y5">
-        <v>-0.1912512001229722</v>
+        <v>-0.2352731911092671</v>
       </c>
       <c r="Z5">
-        <v>0.7205301513461925</v>
+        <v>0.7337858656213775</v>
       </c>
       <c r="AA5">
         <v>9.965784284662087</v>
       </c>
       <c r="AB5">
-        <v>1.218363464633391</v>
+        <v>1.192935124537182</v>
       </c>
       <c r="AC5">
-        <v>1.228020993093113</v>
+        <v>1.218026783767516</v>
       </c>
       <c r="AD5">
         <v>9.965784284662087</v>
       </c>
       <c r="AE5">
-        <v>1.331127024462426</v>
+        <v>1.305156053579741</v>
       </c>
       <c r="AF5">
-        <v>1.884271785758477</v>
+        <v>1.886409443175733</v>
       </c>
       <c r="AG5">
-        <v>1.745967209410987</v>
+        <v>1.742554751161713</v>
       </c>
       <c r="AH5">
         <v>390.6249999999999</v>
@@ -1084,16 +1084,16 @@
         <v>0.0006406406406406406</v>
       </c>
       <c r="AL5">
-        <v>375</v>
+        <v>381.25</v>
       </c>
       <c r="AM5">
-        <v>2.315546464713939E-10</v>
+        <v>3.397505292208282E-10</v>
       </c>
       <c r="AN5">
         <v>300</v>
       </c>
       <c r="AO5">
-        <v>1.049862541187762E-08</v>
+        <v>1.219855321095653E-08</v>
       </c>
     </row>
     <row r="6" spans="1:41">
@@ -1101,58 +1101,58 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>70.23999999999999</v>
+        <v>70.08</v>
       </c>
       <c r="C6">
-        <v>0.004980976642308281</v>
+        <v>0.004894654290807995</v>
       </c>
       <c r="D6">
-        <v>116</v>
+        <v>115.84</v>
       </c>
       <c r="E6">
         <v>37.92</v>
       </c>
       <c r="F6">
-        <v>0.02683053185920529</v>
+        <v>0.02683370302619024</v>
       </c>
       <c r="G6">
         <v>82.55999999999999</v>
       </c>
       <c r="H6">
-        <v>0.4525371913262313</v>
+        <v>0.4503567774359132</v>
       </c>
       <c r="I6">
-        <v>8.968166152835961</v>
+        <v>8.995888903847055</v>
       </c>
       <c r="J6">
-        <v>0.0001133087036957358</v>
+        <v>0.0001142791239949148</v>
       </c>
       <c r="K6">
-        <v>0.01413329518614045</v>
+        <v>0.01417881367877688</v>
       </c>
       <c r="L6">
         <v>285</v>
       </c>
       <c r="M6">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="N6">
-        <v>0.000443411054498282</v>
+        <v>0.0004464789184053274</v>
       </c>
       <c r="O6">
-        <v>2.575906305306628E-05</v>
+        <v>2.626478905332337E-05</v>
       </c>
       <c r="P6">
-        <v>0.2981250566118631</v>
+        <v>0.2983424383279986</v>
       </c>
       <c r="Q6">
-        <v>8.268258179884965</v>
+        <v>8.271568684953762</v>
       </c>
       <c r="R6">
-        <v>9.547595662856386E-06</v>
+        <v>9.469020286026489E-06</v>
       </c>
       <c r="S6">
-        <v>0.01347385611718908</v>
+        <v>0.0134754070101818</v>
       </c>
       <c r="T6">
         <v>278</v>
@@ -1161,40 +1161,40 @@
         <v>515</v>
       </c>
       <c r="V6">
-        <v>0.0009788215948251305</v>
+        <v>0.0009789127113769781</v>
       </c>
       <c r="W6">
-        <v>8.511598585391653E-05</v>
+        <v>8.593715386120968E-05</v>
       </c>
       <c r="X6">
-        <v>-1.343463302451571</v>
+        <v>-1.360963915151898</v>
       </c>
       <c r="Y6">
-        <v>-1.184909562741106</v>
+        <v>-1.183585714816481</v>
       </c>
       <c r="Z6">
-        <v>0.5585532915080137</v>
+        <v>0.5563891097081436</v>
       </c>
       <c r="AA6">
         <v>9.965784284662087</v>
       </c>
       <c r="AB6">
-        <v>1.165901291511937</v>
+        <v>1.167882568717359</v>
       </c>
       <c r="AC6">
-        <v>0.357650338546605</v>
+        <v>0.3576482917025315</v>
       </c>
       <c r="AD6">
         <v>9.965784284662087</v>
       </c>
       <c r="AE6">
-        <v>1.160401512891571</v>
+        <v>1.160110436683702</v>
       </c>
       <c r="AF6">
-        <v>1.870263305875198</v>
+        <v>1.869646772855092</v>
       </c>
       <c r="AG6">
-        <v>1.919659023244198</v>
+        <v>1.919249747006841</v>
       </c>
       <c r="AH6">
         <v>390.6249999999999</v>
@@ -1212,13 +1212,13 @@
         <v>362.5</v>
       </c>
       <c r="AM6">
-        <v>2.451650626910585E-10</v>
+        <v>2.542476401313664E-10</v>
       </c>
       <c r="AN6">
         <v>300</v>
       </c>
       <c r="AO6">
-        <v>1.719581102872684E-09</v>
+        <v>1.763885037763701E-09</v>
       </c>
     </row>
     <row r="7" spans="1:41">
@@ -1229,31 +1229,31 @@
         <v>21.44</v>
       </c>
       <c r="C7">
-        <v>0.02952097900191285</v>
+        <v>0.02963373570230184</v>
       </c>
       <c r="D7">
         <v>68.48</v>
       </c>
       <c r="E7">
-        <v>20.32</v>
+        <v>20.16</v>
       </c>
       <c r="F7">
-        <v>0.0126930232920698</v>
+        <v>0.01272795927245504</v>
       </c>
       <c r="G7">
         <v>70.56</v>
       </c>
       <c r="H7">
-        <v>0.7346740030791319</v>
+        <v>0.7331725181944873</v>
       </c>
       <c r="I7">
-        <v>6.855780169513805</v>
+        <v>6.839505414134049</v>
       </c>
       <c r="J7">
-        <v>3.245736620707301E-05</v>
+        <v>3.351584354836885E-05</v>
       </c>
       <c r="K7">
-        <v>0.01564437683076316</v>
+        <v>0.01570221039507413</v>
       </c>
       <c r="L7">
         <v>293</v>
@@ -1262,64 +1262,64 @@
         <v>427</v>
       </c>
       <c r="N7">
-        <v>0.0005295930856930405</v>
+        <v>0.0005792130529145993</v>
       </c>
       <c r="O7">
-        <v>9.052913858930483E-05</v>
+        <v>0.0001010215796501919</v>
       </c>
       <c r="P7">
-        <v>1.500278613808188</v>
+        <v>1.498473090250327</v>
       </c>
       <c r="Q7">
-        <v>7.829507740666047</v>
+        <v>7.780137733899036</v>
       </c>
       <c r="R7">
-        <v>2.802054242041337E-05</v>
+        <v>2.414069538167809E-05</v>
       </c>
       <c r="S7">
-        <v>0.00677764570747657</v>
+        <v>0.006803961306673538</v>
       </c>
       <c r="T7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="U7">
         <v>440</v>
       </c>
       <c r="V7">
-        <v>0.001332709963639083</v>
+        <v>0.001160429896745191</v>
       </c>
       <c r="W7">
-        <v>4.439594164369012E-06</v>
+        <v>3.361352208650793E-06</v>
       </c>
       <c r="X7">
-        <v>-1.269698071624981</v>
+        <v>-1.273316485229052</v>
       </c>
       <c r="Y7">
-        <v>-0.7200760915669344</v>
+        <v>-0.7195059714363239</v>
       </c>
       <c r="Z7">
-        <v>0.7270176676523481</v>
+        <v>0.7267007050004923</v>
       </c>
       <c r="AA7">
         <v>9.965784284662087</v>
       </c>
       <c r="AB7">
-        <v>1.153114088600127</v>
+        <v>1.153923858880033</v>
       </c>
       <c r="AC7">
-        <v>0.5672737969392552</v>
+        <v>0.5601833647117149</v>
       </c>
       <c r="AD7">
         <v>9.965784284662087</v>
       </c>
       <c r="AE7">
-        <v>1.170549618803507</v>
+        <v>1.158401032305496</v>
       </c>
       <c r="AF7">
-        <v>1.96664353017616</v>
+        <v>1.964534643312794</v>
       </c>
       <c r="AG7">
-        <v>2.038893231648245</v>
+        <v>2.038830688785422</v>
       </c>
       <c r="AH7">
         <v>390.6249999999999</v>
@@ -1337,13 +1337,13 @@
         <v>300</v>
       </c>
       <c r="AM7">
-        <v>2.055247385039394E-09</v>
+        <v>2.447657310048965E-09</v>
       </c>
       <c r="AN7">
         <v>312.5</v>
       </c>
       <c r="AO7">
-        <v>1.639566608964256E-10</v>
+        <v>9.671477385015458E-11</v>
       </c>
     </row>
     <row r="8" spans="1:41">
@@ -1354,31 +1354,31 @@
         <v>30.88</v>
       </c>
       <c r="C8">
-        <v>0.03406822058128589</v>
+        <v>0.03411543781350054</v>
       </c>
       <c r="D8">
         <v>75.2</v>
       </c>
       <c r="E8">
-        <v>40.64</v>
+        <v>40.8</v>
       </c>
       <c r="F8">
-        <v>0.01293806027683731</v>
+        <v>0.01290814174907388</v>
       </c>
       <c r="G8">
-        <v>78.56</v>
+        <v>78.72</v>
       </c>
       <c r="H8">
-        <v>0.4006667190376338</v>
+        <v>0.4037588857976636</v>
       </c>
       <c r="I8">
-        <v>7.505273343150629</v>
+        <v>7.519445805785107</v>
       </c>
       <c r="J8">
-        <v>9.793340573712928E-05</v>
+        <v>9.790545110355836E-05</v>
       </c>
       <c r="K8">
-        <v>0.01731319249915041</v>
+        <v>0.01733765724220214</v>
       </c>
       <c r="L8">
         <v>276</v>
@@ -1387,64 +1387,64 @@
         <v>469</v>
       </c>
       <c r="N8">
-        <v>0.0007298308337529448</v>
+        <v>0.000770496257111267</v>
       </c>
       <c r="O8">
-        <v>6.316190199481711E-05</v>
+        <v>7.117634993294828E-05</v>
       </c>
       <c r="P8">
-        <v>0.1229945835965955</v>
+        <v>0.08471663802105557</v>
       </c>
       <c r="Q8">
-        <v>7.898793633567539</v>
+        <v>7.847449794855663</v>
       </c>
       <c r="R8">
-        <v>7.250255184383614E-05</v>
+        <v>7.224159477059379E-05</v>
       </c>
       <c r="S8">
-        <v>0.006589039886347571</v>
+        <v>0.006574962335496505</v>
       </c>
       <c r="T8">
         <v>236</v>
       </c>
       <c r="U8">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="V8">
-        <v>0.003243779648000234</v>
+        <v>0.003266358420032127</v>
       </c>
       <c r="W8">
-        <v>2.549698974745257E-06</v>
+        <v>2.595270365447613E-06</v>
       </c>
       <c r="X8">
-        <v>-0.1264858932598404</v>
+        <v>-0.1266302694550845</v>
       </c>
       <c r="Y8">
-        <v>-0.7263002106974825</v>
+        <v>-0.7335162789189389</v>
       </c>
       <c r="Z8">
-        <v>0.4626879607771888</v>
+        <v>0.4636864671417764</v>
       </c>
       <c r="AA8">
         <v>9.965784284662087</v>
       </c>
       <c r="AB8">
-        <v>1.221715118999123</v>
+        <v>1.223733804157142</v>
       </c>
       <c r="AC8">
-        <v>0.5205939887913505</v>
+        <v>0.5182263605620913</v>
       </c>
       <c r="AD8">
         <v>9.965784284662087</v>
       </c>
       <c r="AE8">
-        <v>1.170408091742932</v>
+        <v>1.197657566408511</v>
       </c>
       <c r="AF8">
-        <v>1.777054446509016</v>
+        <v>1.776900485181403</v>
       </c>
       <c r="AG8">
-        <v>1.957118712207264</v>
+        <v>1.957236593337508</v>
       </c>
       <c r="AH8">
         <v>390.6249999999999</v>
@@ -1462,13 +1462,13 @@
         <v>425</v>
       </c>
       <c r="AM8">
-        <v>1.441062988329308E-09</v>
+        <v>1.555986452313729E-09</v>
       </c>
       <c r="AN8">
         <v>362.5</v>
       </c>
       <c r="AO8">
-        <v>5.467928470434647E-11</v>
+        <v>5.873634700480806E-11</v>
       </c>
     </row>
     <row r="9" spans="1:41">
@@ -1479,7 +1479,7 @@
         <v>91.67999999999999</v>
       </c>
       <c r="C9">
-        <v>0.002804609079358821</v>
+        <v>0.002803153374685122</v>
       </c>
       <c r="D9">
         <v>136.16</v>
@@ -1488,22 +1488,22 @@
         <v>24.32</v>
       </c>
       <c r="F9">
-        <v>0.016144306175159</v>
+        <v>0.01608519684500757</v>
       </c>
       <c r="G9">
         <v>65.92</v>
       </c>
       <c r="H9">
-        <v>1.583548019554629</v>
+        <v>1.586002915598211</v>
       </c>
       <c r="I9">
-        <v>11.42684882669506</v>
+        <v>11.45077697735511</v>
       </c>
       <c r="J9">
-        <v>1.92005026196985E-05</v>
+        <v>1.911163574776452E-05</v>
       </c>
       <c r="K9">
-        <v>0.008658554904037278</v>
+        <v>0.008677532200829379</v>
       </c>
       <c r="L9">
         <v>277</v>
@@ -1512,22 +1512,22 @@
         <v>850</v>
       </c>
       <c r="N9">
-        <v>0.0003555728408532602</v>
+        <v>0.0003530757473224698</v>
       </c>
       <c r="O9">
-        <v>9.754334591365849E-07</v>
+        <v>8.64609904131469E-07</v>
       </c>
       <c r="P9">
-        <v>-0.05402338115838327</v>
+        <v>-0.05797111319542955</v>
       </c>
       <c r="Q9">
-        <v>4.311377089090295</v>
+        <v>4.264805937978899</v>
       </c>
       <c r="R9">
-        <v>-0.0001051465168284826</v>
+        <v>-0.0001062170339768839</v>
       </c>
       <c r="S9">
-        <v>0.008454296271040681</v>
+        <v>0.00843003356359719</v>
       </c>
       <c r="T9">
         <v>259</v>
@@ -1536,40 +1536,40 @@
         <v>411</v>
       </c>
       <c r="V9">
-        <v>0.0006468615082111331</v>
+        <v>0.0006506982289878632</v>
       </c>
       <c r="W9">
-        <v>2.320053582268403E-05</v>
+        <v>2.327905148019922E-05</v>
       </c>
       <c r="X9">
-        <v>-0.1141383132685594</v>
+        <v>-0.1150938080697775</v>
       </c>
       <c r="Y9">
-        <v>-0.5966701504409082</v>
+        <v>-0.6048480201138513</v>
       </c>
       <c r="Z9">
-        <v>0.714773367023011</v>
+        <v>0.7140088312980793</v>
       </c>
       <c r="AA9">
         <v>9.965784284662087</v>
       </c>
       <c r="AB9">
-        <v>1.150344867297527</v>
+        <v>1.151257907765329</v>
       </c>
       <c r="AC9">
-        <v>0.5794872787573536</v>
+        <v>0.5792640388409001</v>
       </c>
       <c r="AD9">
         <v>9.965784284662087</v>
       </c>
       <c r="AE9">
-        <v>1.235657833786838</v>
+        <v>1.236017103228218</v>
       </c>
       <c r="AF9">
-        <v>1.854921656632994</v>
+        <v>1.855131747222761</v>
       </c>
       <c r="AG9">
-        <v>1.902692101579325</v>
+        <v>1.903101624284804</v>
       </c>
       <c r="AH9">
         <v>390.6249999999999</v>
@@ -1584,16 +1584,16 @@
         <v>0.04868868868868869</v>
       </c>
       <c r="AL9">
-        <v>468.75</v>
+        <v>625</v>
       </c>
       <c r="AM9">
-        <v>1.030616001222443E-11</v>
+        <v>8.508918822525677E-12</v>
       </c>
       <c r="AN9">
         <v>362.5</v>
       </c>
       <c r="AO9">
-        <v>6.835341046508541E-10</v>
+        <v>6.751580348011999E-10</v>
       </c>
     </row>
     <row r="10" spans="1:41">
@@ -1604,7 +1604,7 @@
         <v>21.44</v>
       </c>
       <c r="C10">
-        <v>0.0433385039565104</v>
+        <v>0.04330591496598966</v>
       </c>
       <c r="D10">
         <v>66.55999999999999</v>
@@ -1613,22 +1613,22 @@
         <v>38.08000000000001</v>
       </c>
       <c r="F10">
-        <v>0.0217356272540857</v>
+        <v>0.02179154762489305</v>
       </c>
       <c r="G10">
         <v>80.8</v>
       </c>
       <c r="H10">
-        <v>0.998335252576357</v>
+        <v>0.9980518654395569</v>
       </c>
       <c r="I10">
-        <v>7.976318079681183</v>
+        <v>7.989679351015901</v>
       </c>
       <c r="J10">
-        <v>0.0002933110893888252</v>
+        <v>0.0002934408108811994</v>
       </c>
       <c r="K10">
-        <v>0.02245515896413578</v>
+        <v>0.02243882968883374</v>
       </c>
       <c r="L10">
         <v>281</v>
@@ -1637,22 +1637,22 @@
         <v>415</v>
       </c>
       <c r="N10">
-        <v>0.001383134866819978</v>
+        <v>0.001404840982204779</v>
       </c>
       <c r="O10">
-        <v>4.901229367489552E-05</v>
+        <v>5.134527278315582E-05</v>
       </c>
       <c r="P10">
-        <v>0.9398027709548687</v>
+        <v>0.9284885282809707</v>
       </c>
       <c r="Q10">
-        <v>6.496598040642594</v>
+        <v>6.475555670151431</v>
       </c>
       <c r="R10">
-        <v>0.0001336153169968175</v>
+        <v>0.0001347661560251333</v>
       </c>
       <c r="S10">
-        <v>0.011158815480567</v>
+        <v>0.01118580671901675</v>
       </c>
       <c r="T10">
         <v>266</v>
@@ -1661,40 +1661,40 @@
         <v>504</v>
       </c>
       <c r="V10">
-        <v>0.001881086486130078</v>
+        <v>0.001869497199871253</v>
       </c>
       <c r="W10">
-        <v>7.643116879641553E-06</v>
+        <v>6.097228471993545E-06</v>
       </c>
       <c r="X10">
-        <v>-0.6473135889986615</v>
+        <v>-0.6462021301473235</v>
       </c>
       <c r="Y10">
-        <v>-1.243262006089833</v>
+        <v>-1.246724426806768</v>
       </c>
       <c r="Z10">
-        <v>0.5626785779216068</v>
+        <v>0.5627988840550237</v>
       </c>
       <c r="AA10">
         <v>9.965784284662087</v>
       </c>
       <c r="AB10">
-        <v>1.143287997758899</v>
+        <v>1.145333933610569</v>
       </c>
       <c r="AC10">
-        <v>0.6307564245031441</v>
+        <v>0.6290945373151415</v>
       </c>
       <c r="AD10">
         <v>9.965784284662087</v>
       </c>
       <c r="AE10">
-        <v>1.17274572817694</v>
+        <v>1.162789031281847</v>
       </c>
       <c r="AF10">
-        <v>1.917754904105347</v>
+        <v>1.917874762160956</v>
       </c>
       <c r="AG10">
-        <v>2.004823462164662</v>
+        <v>2.004720070774654</v>
       </c>
       <c r="AH10">
         <v>390.6249999999999</v>
@@ -1712,13 +1712,13 @@
         <v>300</v>
       </c>
       <c r="AM10">
-        <v>5.30827197662145E-09</v>
+        <v>5.428483910687878E-09</v>
       </c>
       <c r="AN10">
-        <v>337.5</v>
+        <v>318.75</v>
       </c>
       <c r="AO10">
-        <v>2.18751583240337E-10</v>
+        <v>2.115903863102791E-10</v>
       </c>
     </row>
   </sheetData>
